--- a/学部-gpr/summary_26_self_prediction.xlsx
+++ b/学部-gpr/summary_26_self_prediction.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\26522\Desktop\新建文件夹\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\26522\Desktop\新建文件夹 (2)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{AFE9456F-D833-4B2D-99AB-D75FE8D7D6F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{311D8EB9-4D4D-4FCC-ACA8-20631F940E15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{77607D82-670B-476D-BEBA-D0B42B098F9B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{792C10EF-E2AE-4CB2-A862-17C31C025DBC}"/>
   </bookViews>
   <sheets>
     <sheet name="summary_26_self_prediction" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="92">
   <si>
     <t>部门名称</t>
   </si>
@@ -46,203 +46,256 @@
     <t>本+研+师+是否公课_差值</t>
   </si>
   <si>
+    <t>本+研+师+公课数量_差值</t>
+  </si>
+  <si>
+    <t>本+研+师+公课学分_预测</t>
+  </si>
+  <si>
+    <t>本+研+师+公课学分_差值</t>
+  </si>
+  <si>
+    <t>本+研+师+留+是否公课_预测</t>
+  </si>
+  <si>
+    <t>本+研+师+留+是否公课_差值</t>
+  </si>
+  <si>
+    <t>本+研+师+留+公课数量_预测</t>
+  </si>
+  <si>
+    <t>本+研+师+留+公课数量_差值</t>
+  </si>
+  <si>
+    <t>本+研+师+长留+公课数量_预测</t>
+  </si>
+  <si>
+    <t>本+研+师+长留+公课数量_差值</t>
+  </si>
+  <si>
+    <t>本+研+师+长留_预测</t>
+  </si>
+  <si>
+    <t>本+研+师+长留_差值</t>
+  </si>
+  <si>
+    <t>本+研+师+留+公课学分_预测</t>
+  </si>
+  <si>
+    <t>本+研+师+留+公课学分_差值</t>
+  </si>
+  <si>
+    <t>本+研+师+长留+公课学分_预测</t>
+  </si>
+  <si>
+    <t>本+研+师+长留+公课学分_差值</t>
+  </si>
+  <si>
+    <t>本+研+师+留_预测</t>
+  </si>
+  <si>
+    <t>本+研+师+留_差值</t>
+  </si>
+  <si>
+    <t>本+研+师+长留+是否公课_预测</t>
+  </si>
+  <si>
+    <t>本+研+师+长留+是否公课_差值</t>
+  </si>
+  <si>
+    <t>折合学生数+是否公课_预测</t>
+  </si>
+  <si>
+    <t>折合学生数+是否公课_差值</t>
+  </si>
+  <si>
+    <t>折合学生数+公课数量_预测</t>
+  </si>
+  <si>
+    <t>折合学生数+公课数量_差值</t>
+  </si>
+  <si>
+    <t>折合学生数+公课学分_预测</t>
+  </si>
+  <si>
+    <t>折合学生数+公课学分_差值</t>
+  </si>
+  <si>
+    <t>折合学生数_预测</t>
+  </si>
+  <si>
+    <t>折合学生数_差值</t>
+  </si>
+  <si>
+    <t>物理科学与工程学院</t>
+  </si>
+  <si>
+    <t>数学科学学院</t>
+  </si>
+  <si>
+    <t>化学科学与工程学院</t>
+  </si>
+  <si>
+    <t>海洋与地球科学学院</t>
+  </si>
+  <si>
+    <t>生命科学与技术学院</t>
+  </si>
+  <si>
+    <t>机械工程与机器人学院</t>
+  </si>
+  <si>
+    <t>测绘与地理信息学院</t>
+  </si>
+  <si>
+    <t>计算机科学与技术学院（软件学院）</t>
+  </si>
+  <si>
+    <t>汽车与能源学院</t>
+  </si>
+  <si>
+    <t>材料科学与工程学院</t>
+  </si>
+  <si>
+    <t>电子与信息工程学院</t>
+  </si>
+  <si>
+    <t>环境科学与工程学院，联合国环境规划署-同济大学环境与可持续发展学院</t>
+  </si>
+  <si>
+    <t>土木工程学院</t>
+  </si>
+  <si>
+    <t>交通学院（铁道与城市轨道交通研究院），未减去磁浮中心的数量</t>
+  </si>
+  <si>
+    <t>建筑与城市规划学院</t>
+  </si>
+  <si>
+    <t>航空航天与力学学院</t>
+  </si>
+  <si>
+    <t>中德工程学院，职业技术教育学院</t>
+  </si>
+  <si>
+    <t>null</t>
+  </si>
+  <si>
+    <t>医学院</t>
+  </si>
+  <si>
+    <t>设计创意学院</t>
+  </si>
+  <si>
+    <t>人文学院</t>
+  </si>
+  <si>
+    <t>外国语学院</t>
+  </si>
+  <si>
+    <t>经济与管理学院</t>
+  </si>
+  <si>
+    <t>政治与国际关系学院</t>
+  </si>
+  <si>
+    <t>艺术与传媒学院</t>
+  </si>
+  <si>
+    <t>上海国际知识产权学院</t>
+  </si>
+  <si>
+    <t>马克思主义学院</t>
+  </si>
+  <si>
+    <t>国际文化交流学院</t>
+  </si>
+  <si>
+    <t>法学院</t>
+  </si>
+  <si>
+    <t>体育部（国际足球学院）</t>
+  </si>
+  <si>
+    <t>医学与生命科学部</t>
+  </si>
+  <si>
+    <t>出国培训学院，留德预备部</t>
+  </si>
+  <si>
+    <t>网络教育学院，继续教育学院</t>
+  </si>
+  <si>
+    <t>中德学院</t>
+  </si>
+  <si>
+    <t>创新创业学院</t>
+  </si>
+  <si>
+    <t>新生院</t>
+  </si>
+  <si>
+    <t>国豪书院（未来技术学院）</t>
+  </si>
+  <si>
+    <t>国家卓越工程师学院，国际工程师学院</t>
+  </si>
+  <si>
+    <t>中意工程创新学院</t>
+  </si>
+  <si>
+    <t>启迪书院</t>
+  </si>
+  <si>
+    <t>口腔医学院</t>
+  </si>
+  <si>
+    <t>上海自主智能无人系统科学中心</t>
+  </si>
+  <si>
+    <t>同济大学上海国际设计创新学院</t>
+  </si>
+  <si>
+    <t>【汇总】R²</t>
+  </si>
+  <si>
+    <t>【汇总】MAPE(%)</t>
+  </si>
+  <si>
+    <t>【汇总】t_p(均值检验)</t>
+  </si>
+  <si>
+    <t>【汇总】均值检验结论</t>
+  </si>
+  <si>
+    <t>通过</t>
+  </si>
+  <si>
+    <t>【汇总】F_p(方差检验)</t>
+  </si>
+  <si>
+    <t>【汇总】方差检验结论</t>
+  </si>
+  <si>
+    <t>【汇总】Levene_p</t>
+  </si>
+  <si>
+    <t>【汇总】Levene检验结论</t>
+  </si>
+  <si>
+    <t>【汇总】MAE_vs参数1(26自预测)</t>
+  </si>
+  <si>
+    <t>【汇总】RMSE_vs参数1(26自预测)</t>
+  </si>
+  <si>
+    <t>【汇总】MAE_vs参数2(26自预测)</t>
+  </si>
+  <si>
+    <t>【汇总】RMSE_vs参数2(26自预测)</t>
+  </si>
+  <si>
     <t>本+研+师+公课数量_预测</t>
-  </si>
-  <si>
-    <t>本+研+师+公课数量_差值</t>
-  </si>
-  <si>
-    <t>本+研+师+公课学分_预测</t>
-  </si>
-  <si>
-    <t>本+研+师+公课学分_差值</t>
-  </si>
-  <si>
-    <t>本+研+师+留+公课学分_预测</t>
-  </si>
-  <si>
-    <t>本+研+师+留+公课学分_差值</t>
-  </si>
-  <si>
-    <t>本+研+师+留+公课数量_预测</t>
-  </si>
-  <si>
-    <t>本+研+师+留+公课数量_差值</t>
-  </si>
-  <si>
-    <t>本+研+师+长留+公课数量_预测</t>
-  </si>
-  <si>
-    <t>本+研+师+长留+公课数量_差值</t>
-  </si>
-  <si>
-    <t>本+研+师+长留+公课学分_预测</t>
-  </si>
-  <si>
-    <t>本+研+师+长留+公课学分_差值</t>
-  </si>
-  <si>
-    <t>本+研+师+留+是否公课_预测</t>
-  </si>
-  <si>
-    <t>本+研+师+留+是否公课_差值</t>
-  </si>
-  <si>
-    <t>本+研+师+长留_预测</t>
-  </si>
-  <si>
-    <t>本+研+师+长留_差值</t>
-  </si>
-  <si>
-    <t>本+研+师+长留+是否公课_预测</t>
-  </si>
-  <si>
-    <t>本+研+师+长留+是否公课_差值</t>
-  </si>
-  <si>
-    <t>本+研+师+留_预测</t>
-  </si>
-  <si>
-    <t>本+研+师+留_差值</t>
-  </si>
-  <si>
-    <t>折合学生数+是否公课_预测</t>
-  </si>
-  <si>
-    <t>折合学生数+是否公课_差值</t>
-  </si>
-  <si>
-    <t>折合学生数+公课数量_预测</t>
-  </si>
-  <si>
-    <t>折合学生数+公课数量_差值</t>
-  </si>
-  <si>
-    <t>折合学生数+公课学分_预测</t>
-  </si>
-  <si>
-    <t>折合学生数+公课学分_差值</t>
-  </si>
-  <si>
-    <t>折合学生数_预测</t>
-  </si>
-  <si>
-    <t>折合学生数_差值</t>
-  </si>
-  <si>
-    <t>物理科学与工程学院</t>
-  </si>
-  <si>
-    <t>数学科学学院</t>
-  </si>
-  <si>
-    <t>化学科学与工程学院</t>
-  </si>
-  <si>
-    <t>海洋与地球科学学院</t>
-  </si>
-  <si>
-    <t>生命科学与技术学院</t>
-  </si>
-  <si>
-    <t>机械工程与机器人学院</t>
-  </si>
-  <si>
-    <t>测绘与地理信息学院</t>
-  </si>
-  <si>
-    <t>计算机科学与技术学院（软件学院）</t>
-  </si>
-  <si>
-    <t>汽车与能源学院</t>
-  </si>
-  <si>
-    <t>材料科学与工程学院</t>
-  </si>
-  <si>
-    <t>电子与信息工程学院</t>
-  </si>
-  <si>
-    <t>环境科学与工程学院，联合国环境规划署-同济大学环境与可持续发展学院</t>
-  </si>
-  <si>
-    <t>土木工程学院</t>
-  </si>
-  <si>
-    <t>交通学院（铁道与城市轨道交通研究院），未减去磁浮中心的数量</t>
-  </si>
-  <si>
-    <t>建筑与城市规划学院</t>
-  </si>
-  <si>
-    <t>航空航天与力学学院</t>
-  </si>
-  <si>
-    <t>医学院</t>
-  </si>
-  <si>
-    <t>设计创意学院</t>
-  </si>
-  <si>
-    <t>人文学院</t>
-  </si>
-  <si>
-    <t>外国语学院</t>
-  </si>
-  <si>
-    <t>经济与管理学院</t>
-  </si>
-  <si>
-    <t>政治与国际关系学院</t>
-  </si>
-  <si>
-    <t>艺术与传媒学院</t>
-  </si>
-  <si>
-    <t>马克思主义学院</t>
-  </si>
-  <si>
-    <t>国际文化交流学院</t>
-  </si>
-  <si>
-    <t>法学院</t>
-  </si>
-  <si>
-    <t>体育部（国际足球学院）</t>
-  </si>
-  <si>
-    <t>【汇总】R²</t>
-  </si>
-  <si>
-    <t>【汇总】MAPE(%)</t>
-  </si>
-  <si>
-    <t>【汇总】t_p(均值检验)</t>
-  </si>
-  <si>
-    <t>【汇总】均值检验结论</t>
-  </si>
-  <si>
-    <t>通过</t>
-  </si>
-  <si>
-    <t>【汇总】F_p(方差检验)</t>
-  </si>
-  <si>
-    <t>【汇总】方差检验结论</t>
-  </si>
-  <si>
-    <t>【汇总】Levene_p</t>
-  </si>
-  <si>
-    <t>【汇总】Levene检验结论</t>
-  </si>
-  <si>
-    <t>【汇总】MAE_vs参数1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>【汇总】MAE_vs参数2</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1203,12 +1256,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CC07AA6-360E-434D-B83F-E5F711CD7A3F}">
-  <dimension ref="A1:AJ38"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96283500-D5BF-4C09-9897-5C07025CECC7}">
+  <dimension ref="A1:AJ55"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="8" width="8.88671875" style="1"/>
-    <col min="15" max="16" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.25">
@@ -1237,93 +1289,93 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
+        <v>91</v>
+      </c>
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>34</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B2">
         <v>10.18</v>
@@ -1335,105 +1387,105 @@
         <v>6</v>
       </c>
       <c r="E2">
+        <v>9.83</v>
+      </c>
+      <c r="F2">
+        <v>-0.34</v>
+      </c>
+      <c r="G2" s="1">
         <v>9.91</v>
       </c>
-      <c r="F2">
+      <c r="H2" s="1">
         <v>-0.27</v>
       </c>
-      <c r="G2" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="H2" s="1">
-        <v>-0.19</v>
-      </c>
       <c r="I2">
-        <v>9.4499999999999993</v>
+        <v>9.2799999999999994</v>
       </c>
       <c r="J2">
-        <v>-0.73</v>
+        <v>-0.9</v>
       </c>
       <c r="K2">
-        <v>9.49</v>
+        <v>9.3800000000000008</v>
       </c>
       <c r="L2">
-        <v>-0.69</v>
+        <v>-0.79</v>
       </c>
       <c r="M2">
-        <v>9.25</v>
+        <v>9.19</v>
       </c>
       <c r="N2">
-        <v>-0.93</v>
-      </c>
-      <c r="O2" s="1">
-        <v>9.14</v>
-      </c>
-      <c r="P2" s="1">
-        <v>-1.04</v>
+        <v>-0.98</v>
+      </c>
+      <c r="O2">
+        <v>9</v>
+      </c>
+      <c r="P2">
+        <v>-1.17</v>
       </c>
       <c r="Q2">
-        <v>9.24</v>
+        <v>9.02</v>
       </c>
       <c r="R2">
-        <v>-0.94</v>
+        <v>-1.1499999999999999</v>
       </c>
       <c r="S2">
-        <v>9.25</v>
+        <v>9.34</v>
       </c>
       <c r="T2">
+        <v>-0.83</v>
+      </c>
+      <c r="U2">
+        <v>9.15</v>
+      </c>
+      <c r="V2">
+        <v>-1.03</v>
+      </c>
+      <c r="W2">
+        <v>9.11</v>
+      </c>
+      <c r="X2">
+        <v>-1.07</v>
+      </c>
+      <c r="Y2">
+        <v>9.26</v>
+      </c>
+      <c r="Z2">
         <v>-0.92</v>
       </c>
-      <c r="U2">
-        <v>9.33</v>
-      </c>
-      <c r="V2">
-        <v>-0.84</v>
-      </c>
-      <c r="W2">
-        <v>9.4700000000000006</v>
-      </c>
-      <c r="X2">
-        <v>-0.7</v>
-      </c>
-      <c r="Y2">
-        <v>9.31</v>
-      </c>
-      <c r="Z2">
-        <v>-0.86</v>
-      </c>
       <c r="AA2">
-        <v>9.2100000000000009</v>
+        <v>9.15</v>
       </c>
       <c r="AB2">
-        <v>-0.96</v>
+        <v>-1.03</v>
       </c>
       <c r="AC2">
-        <v>8.11</v>
+        <v>8.18</v>
       </c>
       <c r="AD2">
-        <v>-2.0699999999999998</v>
+        <v>-2</v>
       </c>
       <c r="AE2">
-        <v>7.33</v>
+        <v>7.48</v>
       </c>
       <c r="AF2">
-        <v>-2.85</v>
+        <v>-2.7</v>
       </c>
       <c r="AG2">
-        <v>8.4</v>
+        <v>8.56</v>
       </c>
       <c r="AH2">
-        <v>-1.77</v>
+        <v>-1.61</v>
       </c>
       <c r="AI2">
-        <v>8.16</v>
+        <v>8.2799999999999994</v>
       </c>
       <c r="AJ2">
-        <v>-2.0099999999999998</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B3">
         <v>7.8</v>
@@ -1445,105 +1497,105 @@
         <v>6</v>
       </c>
       <c r="E3">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="F3">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="G3" s="1">
-        <v>7.18</v>
+        <v>7.1</v>
       </c>
       <c r="H3" s="1">
-        <v>-0.62</v>
+        <v>-0.71</v>
       </c>
       <c r="I3">
-        <v>7.41</v>
+        <v>7.45</v>
       </c>
       <c r="J3">
-        <v>-0.4</v>
+        <v>-0.36</v>
       </c>
       <c r="K3">
-        <v>6.53</v>
+        <v>6.49</v>
       </c>
       <c r="L3">
-        <v>-1.27</v>
+        <v>-1.31</v>
       </c>
       <c r="M3">
-        <v>6.7</v>
+        <v>7.07</v>
       </c>
       <c r="N3">
-        <v>-1.1100000000000001</v>
-      </c>
-      <c r="O3" s="1">
-        <v>7.57</v>
-      </c>
-      <c r="P3" s="1">
-        <v>-0.24</v>
+        <v>-0.74</v>
+      </c>
+      <c r="O3">
+        <v>7.61</v>
+      </c>
+      <c r="P3">
+        <v>-0.19</v>
       </c>
       <c r="Q3">
-        <v>7.44</v>
+        <v>7.51</v>
       </c>
       <c r="R3">
-        <v>-0.36</v>
+        <v>-0.28999999999999998</v>
       </c>
       <c r="S3">
-        <v>6.64</v>
+        <v>7.25</v>
       </c>
       <c r="T3">
-        <v>-1.1599999999999999</v>
+        <v>-0.56000000000000005</v>
       </c>
       <c r="U3">
-        <v>7.14</v>
+        <v>6.66</v>
       </c>
       <c r="V3">
-        <v>-0.66</v>
+        <v>-1.1499999999999999</v>
       </c>
       <c r="W3">
-        <v>7.24</v>
+        <v>6.62</v>
       </c>
       <c r="X3">
-        <v>-0.56000000000000005</v>
+        <v>-1.19</v>
       </c>
       <c r="Y3">
-        <v>7.11</v>
+        <v>7.1</v>
       </c>
       <c r="Z3">
-        <v>-0.69</v>
+        <v>-0.7</v>
       </c>
       <c r="AA3">
-        <v>7.24</v>
+        <v>7.06</v>
       </c>
       <c r="AB3">
-        <v>-0.56999999999999995</v>
+        <v>-0.75</v>
       </c>
       <c r="AC3">
-        <v>7.21</v>
+        <v>7.17</v>
       </c>
       <c r="AD3">
-        <v>-0.59</v>
+        <v>-0.63</v>
       </c>
       <c r="AE3">
-        <v>8.7200000000000006</v>
+        <v>8.67</v>
       </c>
       <c r="AF3">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="AG3">
-        <v>6.79</v>
+        <v>6.6</v>
       </c>
       <c r="AH3">
-        <v>-1.02</v>
+        <v>-1.21</v>
       </c>
       <c r="AI3">
-        <v>7.14</v>
+        <v>6.57</v>
       </c>
       <c r="AJ3">
-        <v>-0.67</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B4">
         <v>6.69</v>
@@ -1555,105 +1607,105 @@
         <v>7</v>
       </c>
       <c r="E4">
-        <v>6.69</v>
+        <v>6.96</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="G4" s="1">
-        <v>6.5</v>
+        <v>6.73</v>
       </c>
       <c r="H4" s="1">
-        <v>-0.19</v>
+        <v>0.04</v>
       </c>
       <c r="I4">
+        <v>6.8</v>
+      </c>
+      <c r="J4">
+        <v>0.11</v>
+      </c>
+      <c r="K4">
+        <v>6.96</v>
+      </c>
+      <c r="L4">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="M4">
+        <v>6.71</v>
+      </c>
+      <c r="N4">
+        <v>0.02</v>
+      </c>
+      <c r="O4">
+        <v>6.78</v>
+      </c>
+      <c r="P4">
+        <v>0.09</v>
+      </c>
+      <c r="Q4">
+        <v>6.84</v>
+      </c>
+      <c r="R4">
+        <v>0.15</v>
+      </c>
+      <c r="S4">
+        <v>6.95</v>
+      </c>
+      <c r="T4">
+        <v>0.26</v>
+      </c>
+      <c r="U4">
+        <v>6.95</v>
+      </c>
+      <c r="V4">
+        <v>0.26</v>
+      </c>
+      <c r="W4">
+        <v>6.96</v>
+      </c>
+      <c r="X4">
+        <v>0.27</v>
+      </c>
+      <c r="Y4">
+        <v>6.73</v>
+      </c>
+      <c r="Z4">
+        <v>0.05</v>
+      </c>
+      <c r="AA4">
+        <v>6.73</v>
+      </c>
+      <c r="AB4">
+        <v>0.04</v>
+      </c>
+      <c r="AC4">
+        <v>7.17</v>
+      </c>
+      <c r="AD4">
+        <v>0.48</v>
+      </c>
+      <c r="AE4">
+        <v>6.58</v>
+      </c>
+      <c r="AF4">
+        <v>-0.11</v>
+      </c>
+      <c r="AG4">
+        <v>7.48</v>
+      </c>
+      <c r="AH4">
+        <v>0.79</v>
+      </c>
+      <c r="AI4">
         <v>6.57</v>
       </c>
-      <c r="J4">
+      <c r="AJ4">
         <v>-0.12</v>
-      </c>
-      <c r="K4">
-        <v>6.62</v>
-      </c>
-      <c r="L4">
-        <v>-7.0000000000000007E-2</v>
-      </c>
-      <c r="M4">
-        <v>6.61</v>
-      </c>
-      <c r="N4">
-        <v>-0.08</v>
-      </c>
-      <c r="O4" s="1">
-        <v>6.54</v>
-      </c>
-      <c r="P4" s="1">
-        <v>-0.15</v>
-      </c>
-      <c r="Q4">
-        <v>6.6</v>
-      </c>
-      <c r="R4">
-        <v>-0.08</v>
-      </c>
-      <c r="S4">
-        <v>6.61</v>
-      </c>
-      <c r="T4">
-        <v>-0.08</v>
-      </c>
-      <c r="U4">
-        <v>6.5</v>
-      </c>
-      <c r="V4">
-        <v>-0.19</v>
-      </c>
-      <c r="W4">
-        <v>6.64</v>
-      </c>
-      <c r="X4">
-        <v>-0.05</v>
-      </c>
-      <c r="Y4">
-        <v>6.56</v>
-      </c>
-      <c r="Z4">
-        <v>-0.13</v>
-      </c>
-      <c r="AA4">
-        <v>6.43</v>
-      </c>
-      <c r="AB4">
-        <v>-0.25</v>
-      </c>
-      <c r="AC4">
-        <v>7.21</v>
-      </c>
-      <c r="AD4">
-        <v>0.53</v>
-      </c>
-      <c r="AE4">
-        <v>6.51</v>
-      </c>
-      <c r="AF4">
-        <v>-0.17</v>
-      </c>
-      <c r="AG4">
-        <v>7.44</v>
-      </c>
-      <c r="AH4">
-        <v>0.75</v>
-      </c>
-      <c r="AI4">
-        <v>7.14</v>
-      </c>
-      <c r="AJ4">
-        <v>0.45</v>
       </c>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B5">
         <v>7.93</v>
@@ -1665,105 +1717,105 @@
         <v>8</v>
       </c>
       <c r="E5">
-        <v>7.98</v>
+        <v>8.19</v>
       </c>
       <c r="F5">
-        <v>0.05</v>
+        <v>0.26</v>
       </c>
       <c r="G5" s="1">
-        <v>8.2799999999999994</v>
+        <v>8.4700000000000006</v>
       </c>
       <c r="H5" s="1">
-        <v>0.34</v>
+        <v>0.54</v>
       </c>
       <c r="I5">
-        <v>8.1999999999999993</v>
+        <v>8.3699999999999992</v>
       </c>
       <c r="J5">
-        <v>0.26</v>
+        <v>0.43</v>
       </c>
       <c r="K5">
-        <v>8.32</v>
+        <v>8.4499999999999993</v>
       </c>
       <c r="L5">
-        <v>0.39</v>
+        <v>0.52</v>
       </c>
       <c r="M5">
+        <v>8.24</v>
+      </c>
+      <c r="N5">
+        <v>0.31</v>
+      </c>
+      <c r="O5">
+        <v>7.95</v>
+      </c>
+      <c r="P5">
+        <v>0.01</v>
+      </c>
+      <c r="Q5">
+        <v>8.06</v>
+      </c>
+      <c r="R5">
+        <v>0.12</v>
+      </c>
+      <c r="S5">
+        <v>8.06</v>
+      </c>
+      <c r="T5">
+        <v>0.13</v>
+      </c>
+      <c r="U5">
+        <v>8.0500000000000007</v>
+      </c>
+      <c r="V5">
+        <v>0.12</v>
+      </c>
+      <c r="W5">
+        <v>8.17</v>
+      </c>
+      <c r="X5">
+        <v>0.24</v>
+      </c>
+      <c r="Y5">
         <v>8.01</v>
       </c>
-      <c r="N5">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="O5" s="1">
-        <v>7.88</v>
-      </c>
-      <c r="P5" s="1">
-        <v>-0.06</v>
-      </c>
-      <c r="Q5">
-        <v>7.94</v>
-      </c>
-      <c r="R5">
-        <v>0.01</v>
-      </c>
-      <c r="S5">
-        <v>8.08</v>
-      </c>
-      <c r="T5">
-        <v>0.15</v>
-      </c>
-      <c r="U5">
-        <v>8.16</v>
-      </c>
-      <c r="V5">
-        <v>0.23</v>
-      </c>
-      <c r="W5">
-        <v>7.96</v>
-      </c>
-      <c r="X5">
-        <v>0.03</v>
-      </c>
-      <c r="Y5">
-        <v>8.2100000000000009</v>
-      </c>
       <c r="Z5">
-        <v>0.27</v>
+        <v>0.08</v>
       </c>
       <c r="AA5">
-        <v>7.85</v>
+        <v>8.3800000000000008</v>
       </c>
       <c r="AB5">
-        <v>-0.08</v>
+        <v>0.44</v>
       </c>
       <c r="AC5">
-        <v>7.13</v>
+        <v>6.08</v>
       </c>
       <c r="AD5">
-        <v>-0.8</v>
+        <v>-1.85</v>
       </c>
       <c r="AE5">
-        <v>6.92</v>
+        <v>6.13</v>
       </c>
       <c r="AF5">
-        <v>-1.01</v>
+        <v>-1.81</v>
       </c>
       <c r="AG5">
-        <v>6.86</v>
+        <v>6.02</v>
       </c>
       <c r="AH5">
-        <v>-1.07</v>
+        <v>-1.91</v>
       </c>
       <c r="AI5">
-        <v>7.01</v>
+        <v>6.27</v>
       </c>
       <c r="AJ5">
-        <v>-0.92</v>
+        <v>-1.66</v>
       </c>
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B6">
         <v>9.98</v>
@@ -1775,40 +1827,40 @@
         <v>8</v>
       </c>
       <c r="E6">
-        <v>10.029999999999999</v>
+        <v>10.210000000000001</v>
       </c>
       <c r="F6">
-        <v>0.05</v>
+        <v>0.23</v>
       </c>
       <c r="G6" s="1">
-        <v>10.25</v>
+        <v>10.47</v>
       </c>
       <c r="H6" s="1">
-        <v>0.27</v>
+        <v>0.49</v>
       </c>
       <c r="I6">
-        <v>10.32</v>
+        <v>10.45</v>
       </c>
       <c r="J6">
-        <v>0.34</v>
+        <v>0.47</v>
       </c>
       <c r="K6">
-        <v>10.43</v>
+        <v>10.5</v>
       </c>
       <c r="L6">
-        <v>0.45</v>
+        <v>0.52</v>
       </c>
       <c r="M6">
-        <v>9.81</v>
+        <v>9.9499999999999993</v>
       </c>
       <c r="N6">
-        <v>-0.17</v>
-      </c>
-      <c r="O6" s="1">
-        <v>9.69</v>
-      </c>
-      <c r="P6" s="1">
-        <v>-0.28999999999999998</v>
+        <v>-0.03</v>
+      </c>
+      <c r="O6">
+        <v>9.68</v>
+      </c>
+      <c r="P6">
+        <v>-0.3</v>
       </c>
       <c r="Q6">
         <v>9.76</v>
@@ -1817,63 +1869,63 @@
         <v>-0.22</v>
       </c>
       <c r="S6">
-        <v>9.89</v>
+        <v>9.67</v>
       </c>
       <c r="T6">
-        <v>-0.09</v>
+        <v>-0.31</v>
       </c>
       <c r="U6">
-        <v>9.91</v>
+        <v>9.75</v>
       </c>
       <c r="V6">
-        <v>-7.0000000000000007E-2</v>
+        <v>-0.23</v>
       </c>
       <c r="W6">
-        <v>9.67</v>
+        <v>9.85</v>
       </c>
       <c r="X6">
-        <v>-0.31</v>
+        <v>-0.13</v>
       </c>
       <c r="Y6">
-        <v>9.98</v>
+        <v>9.61</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>-0.37</v>
       </c>
       <c r="AA6">
-        <v>9.2799999999999994</v>
+        <v>10.09</v>
       </c>
       <c r="AB6">
-        <v>-0.7</v>
+        <v>0.11</v>
       </c>
       <c r="AC6">
-        <v>9.01</v>
+        <v>8.2899999999999991</v>
       </c>
       <c r="AD6">
-        <v>-0.97</v>
+        <v>-1.69</v>
       </c>
       <c r="AE6">
-        <v>8.89</v>
+        <v>8.43</v>
       </c>
       <c r="AF6">
-        <v>-1.0900000000000001</v>
+        <v>-1.55</v>
       </c>
       <c r="AG6">
-        <v>8.6199999999999992</v>
+        <v>8.26</v>
       </c>
       <c r="AH6">
-        <v>-1.36</v>
+        <v>-1.72</v>
       </c>
       <c r="AI6">
-        <v>8.18</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="AJ6">
-        <v>-1.8</v>
+        <v>-1.68</v>
       </c>
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B7">
         <v>9.49</v>
@@ -1885,105 +1937,105 @@
         <v>11</v>
       </c>
       <c r="E7">
+        <v>9.14</v>
+      </c>
+      <c r="F7">
+        <v>-0.35</v>
+      </c>
+      <c r="G7" s="1">
+        <v>9.2799999999999994</v>
+      </c>
+      <c r="H7" s="1">
+        <v>-0.2</v>
+      </c>
+      <c r="I7">
+        <v>9.02</v>
+      </c>
+      <c r="J7">
+        <v>-0.47</v>
+      </c>
+      <c r="K7">
+        <v>9.08</v>
+      </c>
+      <c r="L7">
+        <v>-0.41</v>
+      </c>
+      <c r="M7">
+        <v>8.92</v>
+      </c>
+      <c r="N7">
+        <v>-0.56999999999999995</v>
+      </c>
+      <c r="O7">
         <v>8.9600000000000009</v>
       </c>
-      <c r="F7">
-        <v>-0.52</v>
-      </c>
-      <c r="G7" s="1">
-        <v>9.15</v>
-      </c>
-      <c r="H7" s="1">
-        <v>-0.33</v>
-      </c>
-      <c r="I7">
-        <v>8.85</v>
-      </c>
-      <c r="J7">
-        <v>-0.64</v>
-      </c>
-      <c r="K7">
-        <v>8.84</v>
-      </c>
-      <c r="L7">
-        <v>-0.65</v>
-      </c>
-      <c r="M7">
-        <v>8.84</v>
-      </c>
-      <c r="N7">
-        <v>-0.65</v>
-      </c>
-      <c r="O7" s="1">
-        <v>8.83</v>
-      </c>
-      <c r="P7" s="1">
-        <v>-0.66</v>
+      <c r="P7">
+        <v>-0.53</v>
       </c>
       <c r="Q7">
-        <v>8.86</v>
+        <v>9.1</v>
       </c>
       <c r="R7">
-        <v>-0.63</v>
+        <v>-0.39</v>
       </c>
       <c r="S7">
-        <v>8.85</v>
+        <v>9.2200000000000006</v>
       </c>
       <c r="T7">
-        <v>-0.63</v>
+        <v>-0.27</v>
       </c>
       <c r="U7">
-        <v>8.7799999999999994</v>
+        <v>9.0500000000000007</v>
       </c>
       <c r="V7">
-        <v>-0.71</v>
+        <v>-0.44</v>
       </c>
       <c r="W7">
-        <v>8.8800000000000008</v>
+        <v>9.18</v>
       </c>
       <c r="X7">
-        <v>-0.61</v>
+        <v>-0.31</v>
       </c>
       <c r="Y7">
-        <v>8.8000000000000007</v>
+        <v>8.9600000000000009</v>
       </c>
       <c r="Z7">
-        <v>-0.69</v>
+        <v>-0.53</v>
       </c>
       <c r="AA7">
-        <v>8.84</v>
+        <v>9</v>
       </c>
       <c r="AB7">
-        <v>-0.65</v>
+        <v>-0.49</v>
       </c>
       <c r="AC7">
-        <v>11.35</v>
+        <v>11.48</v>
       </c>
       <c r="AD7">
-        <v>1.86</v>
+        <v>1.99</v>
       </c>
       <c r="AE7">
-        <v>10.79</v>
+        <v>11.05</v>
       </c>
       <c r="AF7">
-        <v>1.3</v>
+        <v>1.56</v>
       </c>
       <c r="AG7">
-        <v>10.25</v>
+        <v>10.59</v>
       </c>
       <c r="AH7">
-        <v>0.77</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="AI7">
-        <v>11.89</v>
+        <v>12.37</v>
       </c>
       <c r="AJ7">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B8">
         <v>6.46</v>
@@ -1995,105 +2047,105 @@
         <v>5</v>
       </c>
       <c r="E8">
+        <v>6.6</v>
+      </c>
+      <c r="F8">
+        <v>0.13</v>
+      </c>
+      <c r="G8" s="1">
         <v>6.39</v>
       </c>
-      <c r="F8">
-        <v>-7.0000000000000007E-2</v>
-      </c>
-      <c r="G8" s="1">
-        <v>6.2</v>
-      </c>
       <c r="H8" s="1">
-        <v>-0.27</v>
+        <v>-0.08</v>
       </c>
       <c r="I8">
-        <v>6.54</v>
+        <v>6.85</v>
       </c>
       <c r="J8">
-        <v>0.08</v>
+        <v>0.38</v>
       </c>
       <c r="K8">
+        <v>6.94</v>
+      </c>
+      <c r="L8">
+        <v>0.48</v>
+      </c>
+      <c r="M8">
+        <v>6.5</v>
+      </c>
+      <c r="N8">
+        <v>0.03</v>
+      </c>
+      <c r="O8">
+        <v>6.62</v>
+      </c>
+      <c r="P8">
+        <v>0.16</v>
+      </c>
+      <c r="Q8">
+        <v>6.72</v>
+      </c>
+      <c r="R8">
+        <v>0.26</v>
+      </c>
+      <c r="S8">
         <v>6.64</v>
       </c>
-      <c r="L8">
+      <c r="T8">
         <v>0.17</v>
       </c>
-      <c r="M8">
-        <v>6.46</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8" s="1">
-        <v>6.38</v>
-      </c>
-      <c r="P8" s="1">
-        <v>-0.08</v>
-      </c>
-      <c r="Q8">
-        <v>6.38</v>
-      </c>
-      <c r="R8">
-        <v>-0.09</v>
-      </c>
-      <c r="S8">
+      <c r="U8">
+        <v>6.71</v>
+      </c>
+      <c r="V8">
+        <v>0.25</v>
+      </c>
+      <c r="W8">
+        <v>6.84</v>
+      </c>
+      <c r="X8">
+        <v>0.38</v>
+      </c>
+      <c r="Y8">
         <v>6.47</v>
       </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>6.28</v>
-      </c>
-      <c r="V8">
-        <v>-0.19</v>
-      </c>
-      <c r="W8">
-        <v>6.31</v>
-      </c>
-      <c r="X8">
-        <v>-0.15</v>
-      </c>
-      <c r="Y8">
-        <v>6.24</v>
-      </c>
       <c r="Z8">
-        <v>-0.23</v>
+        <v>0.01</v>
       </c>
       <c r="AA8">
-        <v>6.18</v>
+        <v>6.43</v>
       </c>
       <c r="AB8">
-        <v>-0.28000000000000003</v>
+        <v>-0.04</v>
       </c>
       <c r="AC8">
-        <v>7.33</v>
+        <v>7.31</v>
       </c>
       <c r="AD8">
-        <v>0.86</v>
+        <v>0.84</v>
       </c>
       <c r="AE8">
-        <v>7.09</v>
+        <v>6.65</v>
       </c>
       <c r="AF8">
-        <v>0.63</v>
+        <v>0.18</v>
       </c>
       <c r="AG8">
-        <v>6.98</v>
+        <v>6.52</v>
       </c>
       <c r="AH8">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="AI8">
-        <v>7.26</v>
+        <v>6.83</v>
       </c>
       <c r="AJ8">
-        <v>0.8</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B9">
         <v>14.39</v>
@@ -2105,105 +2157,105 @@
         <v>12</v>
       </c>
       <c r="E9">
-        <v>12.37</v>
+        <v>12.6</v>
       </c>
       <c r="F9">
-        <v>-2.0299999999999998</v>
+        <v>-1.8</v>
       </c>
       <c r="G9" s="1">
-        <v>12.57</v>
+        <v>12.73</v>
       </c>
       <c r="H9" s="1">
-        <v>-1.82</v>
+        <v>-1.66</v>
       </c>
       <c r="I9">
-        <v>11.78</v>
+        <v>11.76</v>
       </c>
       <c r="J9">
-        <v>-2.61</v>
+        <v>-2.64</v>
       </c>
       <c r="K9">
-        <v>11.96</v>
+        <v>12.03</v>
       </c>
       <c r="L9">
-        <v>-2.4300000000000002</v>
+        <v>-2.36</v>
       </c>
       <c r="M9">
-        <v>12.2</v>
+        <v>12.6</v>
       </c>
       <c r="N9">
-        <v>-2.2000000000000002</v>
-      </c>
-      <c r="O9" s="1">
-        <v>11.99</v>
-      </c>
-      <c r="P9" s="1">
-        <v>-2.4</v>
+        <v>-1.79</v>
+      </c>
+      <c r="O9">
+        <v>12</v>
+      </c>
+      <c r="P9">
+        <v>-2.39</v>
       </c>
       <c r="Q9">
-        <v>12.05</v>
+        <v>12.08</v>
       </c>
       <c r="R9">
-        <v>-2.34</v>
+        <v>-2.31</v>
       </c>
       <c r="S9">
-        <v>12.21</v>
+        <v>12.84</v>
       </c>
       <c r="T9">
-        <v>-2.19</v>
+        <v>-1.55</v>
       </c>
       <c r="U9">
-        <v>12.46</v>
+        <v>12.28</v>
       </c>
       <c r="V9">
-        <v>-1.93</v>
+        <v>-2.11</v>
       </c>
       <c r="W9">
-        <v>12.51</v>
+        <v>12.33</v>
       </c>
       <c r="X9">
-        <v>-1.88</v>
+        <v>-2.06</v>
       </c>
       <c r="Y9">
-        <v>12.41</v>
+        <v>12.81</v>
       </c>
       <c r="Z9">
-        <v>-1.98</v>
+        <v>-1.58</v>
       </c>
       <c r="AA9">
-        <v>12.62</v>
+        <v>12.59</v>
       </c>
       <c r="AB9">
-        <v>-1.78</v>
+        <v>-1.81</v>
       </c>
       <c r="AC9">
-        <v>14.59</v>
+        <v>14.67</v>
       </c>
       <c r="AD9">
-        <v>0.19</v>
+        <v>0.27</v>
       </c>
       <c r="AE9">
-        <v>11.38</v>
+        <v>11.32</v>
       </c>
       <c r="AF9">
-        <v>-3.02</v>
+        <v>-3.07</v>
       </c>
       <c r="AG9">
-        <v>11.6</v>
+        <v>11.59</v>
       </c>
       <c r="AH9">
-        <v>-2.79</v>
+        <v>-2.8</v>
       </c>
       <c r="AI9">
-        <v>15.48</v>
+        <v>15.6</v>
       </c>
       <c r="AJ9">
-        <v>1.0900000000000001</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B10">
         <v>13.65</v>
@@ -2215,28 +2267,28 @@
         <v>11</v>
       </c>
       <c r="E10">
-        <v>13.62</v>
+        <v>13.72</v>
       </c>
       <c r="F10">
-        <v>-0.03</v>
+        <v>0.08</v>
       </c>
       <c r="G10" s="1">
-        <v>13.35</v>
+        <v>13.7</v>
       </c>
       <c r="H10" s="1">
-        <v>-0.3</v>
+        <v>0.05</v>
       </c>
       <c r="I10">
-        <v>13.93</v>
+        <v>14.08</v>
       </c>
       <c r="J10">
-        <v>0.28999999999999998</v>
+        <v>0.43</v>
       </c>
       <c r="K10">
-        <v>13.85</v>
+        <v>13.99</v>
       </c>
       <c r="L10">
-        <v>0.2</v>
+        <v>0.34</v>
       </c>
       <c r="M10">
         <v>12.81</v>
@@ -2244,76 +2296,76 @@
       <c r="N10">
         <v>-0.84</v>
       </c>
-      <c r="O10" s="1">
-        <v>12.87</v>
-      </c>
-      <c r="P10" s="1">
-        <v>-0.77</v>
+      <c r="O10">
+        <v>12.75</v>
+      </c>
+      <c r="P10">
+        <v>-0.89</v>
       </c>
       <c r="Q10">
+        <v>12.84</v>
+      </c>
+      <c r="R10">
+        <v>-0.81</v>
+      </c>
+      <c r="S10">
+        <v>12.43</v>
+      </c>
+      <c r="T10">
+        <v>-1.22</v>
+      </c>
+      <c r="U10">
+        <v>12.67</v>
+      </c>
+      <c r="V10">
+        <v>-0.98</v>
+      </c>
+      <c r="W10">
         <v>12.79</v>
       </c>
-      <c r="R10">
+      <c r="X10">
         <v>-0.85</v>
       </c>
-      <c r="S10">
-        <v>12.77</v>
-      </c>
-      <c r="T10">
-        <v>-0.88</v>
-      </c>
-      <c r="U10">
-        <v>12.72</v>
-      </c>
-      <c r="V10">
-        <v>-0.93</v>
-      </c>
-      <c r="W10">
-        <v>12.41</v>
-      </c>
-      <c r="X10">
-        <v>-1.24</v>
-      </c>
       <c r="Y10">
-        <v>12.81</v>
+        <v>12.27</v>
       </c>
       <c r="Z10">
-        <v>-0.84</v>
+        <v>-1.38</v>
       </c>
       <c r="AA10">
-        <v>12.16</v>
+        <v>13.01</v>
       </c>
       <c r="AB10">
-        <v>-1.49</v>
+        <v>-0.64</v>
       </c>
       <c r="AC10">
-        <v>16.059999999999999</v>
+        <v>15.91</v>
       </c>
       <c r="AD10">
-        <v>2.41</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="AE10">
-        <v>16.47</v>
+        <v>16.350000000000001</v>
       </c>
       <c r="AF10">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="AG10">
-        <v>16.559999999999999</v>
+        <v>16.52</v>
       </c>
       <c r="AH10">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
       <c r="AI10">
-        <v>15.3</v>
+        <v>15.45</v>
       </c>
       <c r="AJ10">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B11">
         <v>9.59</v>
@@ -2325,105 +2377,105 @@
         <v>9</v>
       </c>
       <c r="E11">
-        <v>9.41</v>
+        <v>9.6</v>
       </c>
       <c r="F11">
-        <v>-0.17</v>
+        <v>0.01</v>
       </c>
       <c r="G11" s="1">
-        <v>9.59</v>
+        <v>9.75</v>
       </c>
       <c r="H11" s="1">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="I11">
-        <v>9.73</v>
+        <v>9.92</v>
       </c>
       <c r="J11">
-        <v>0.14000000000000001</v>
+        <v>0.33</v>
       </c>
       <c r="K11">
-        <v>9.82</v>
+        <v>9.9700000000000006</v>
       </c>
       <c r="L11">
-        <v>0.24</v>
+        <v>0.39</v>
       </c>
       <c r="M11">
+        <v>9.01</v>
+      </c>
+      <c r="N11">
+        <v>-0.56999999999999995</v>
+      </c>
+      <c r="O11">
+        <v>9.24</v>
+      </c>
+      <c r="P11">
+        <v>-0.35</v>
+      </c>
+      <c r="Q11">
+        <v>9.4</v>
+      </c>
+      <c r="R11">
+        <v>-0.18</v>
+      </c>
+      <c r="S11">
+        <v>9.23</v>
+      </c>
+      <c r="T11">
+        <v>-0.35</v>
+      </c>
+      <c r="U11">
+        <v>9.2899999999999991</v>
+      </c>
+      <c r="V11">
+        <v>-0.28999999999999998</v>
+      </c>
+      <c r="W11">
+        <v>9.49</v>
+      </c>
+      <c r="X11">
+        <v>-0.09</v>
+      </c>
+      <c r="Y11">
+        <v>9.01</v>
+      </c>
+      <c r="Z11">
+        <v>-0.57999999999999996</v>
+      </c>
+      <c r="AA11">
+        <v>9.0500000000000007</v>
+      </c>
+      <c r="AB11">
+        <v>-0.54</v>
+      </c>
+      <c r="AC11">
+        <v>8.89</v>
+      </c>
+      <c r="AD11">
+        <v>-0.69</v>
+      </c>
+      <c r="AE11">
+        <v>9.43</v>
+      </c>
+      <c r="AF11">
+        <v>-0.16</v>
+      </c>
+      <c r="AG11">
         <v>9.26</v>
       </c>
-      <c r="N11">
-        <v>-0.32</v>
-      </c>
-      <c r="O11" s="1">
-        <v>9.17</v>
-      </c>
-      <c r="P11" s="1">
-        <v>-0.42</v>
-      </c>
-      <c r="Q11">
-        <v>9.2899999999999991</v>
-      </c>
-      <c r="R11">
-        <v>-0.28999999999999998</v>
-      </c>
-      <c r="S11">
-        <v>9.39</v>
-      </c>
-      <c r="T11">
-        <v>-0.19</v>
-      </c>
-      <c r="U11">
-        <v>8.93</v>
-      </c>
-      <c r="V11">
-        <v>-0.66</v>
-      </c>
-      <c r="W11">
-        <v>9.1300000000000008</v>
-      </c>
-      <c r="X11">
-        <v>-0.45</v>
-      </c>
-      <c r="Y11">
-        <v>9.0299999999999994</v>
-      </c>
-      <c r="Z11">
-        <v>-0.56000000000000005</v>
-      </c>
-      <c r="AA11">
-        <v>8.58</v>
-      </c>
-      <c r="AB11">
-        <v>-1</v>
-      </c>
-      <c r="AC11">
-        <v>8.7899999999999991</v>
-      </c>
-      <c r="AD11">
-        <v>-0.8</v>
-      </c>
-      <c r="AE11">
-        <v>9.67</v>
-      </c>
-      <c r="AF11">
-        <v>0.09</v>
-      </c>
-      <c r="AG11">
-        <v>9.41</v>
-      </c>
       <c r="AH11">
-        <v>-0.18</v>
+        <v>-0.33</v>
       </c>
       <c r="AI11">
-        <v>8.9499999999999993</v>
+        <v>9.2799999999999994</v>
       </c>
       <c r="AJ11">
-        <v>-0.64</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B12">
         <v>21.17</v>
@@ -2435,105 +2487,105 @@
         <v>16</v>
       </c>
       <c r="E12">
-        <v>17.07</v>
+        <v>17.18</v>
       </c>
       <c r="F12">
+        <v>-3.99</v>
+      </c>
+      <c r="G12" s="1">
+        <v>17.54</v>
+      </c>
+      <c r="H12" s="1">
+        <v>-3.63</v>
+      </c>
+      <c r="I12">
+        <v>17.739999999999998</v>
+      </c>
+      <c r="J12">
+        <v>-3.42</v>
+      </c>
+      <c r="K12">
+        <v>17.73</v>
+      </c>
+      <c r="L12">
+        <v>-3.43</v>
+      </c>
+      <c r="M12">
+        <v>17.2</v>
+      </c>
+      <c r="N12">
+        <v>-3.97</v>
+      </c>
+      <c r="O12">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="P12">
+        <v>-3.76</v>
+      </c>
+      <c r="Q12">
+        <v>17.29</v>
+      </c>
+      <c r="R12">
+        <v>-3.88</v>
+      </c>
+      <c r="S12">
+        <v>17</v>
+      </c>
+      <c r="T12">
+        <v>-4.16</v>
+      </c>
+      <c r="U12">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="V12">
+        <v>-3.76</v>
+      </c>
+      <c r="W12">
+        <v>17.350000000000001</v>
+      </c>
+      <c r="X12">
+        <v>-3.82</v>
+      </c>
+      <c r="Y12">
+        <v>17.059999999999999</v>
+      </c>
+      <c r="Z12">
         <v>-4.0999999999999996</v>
       </c>
-      <c r="G12" s="1">
-        <v>17.329999999999998</v>
-      </c>
-      <c r="H12" s="1">
-        <v>-3.83</v>
-      </c>
-      <c r="I12">
-        <v>17.579999999999998</v>
-      </c>
-      <c r="J12">
-        <v>-3.58</v>
-      </c>
-      <c r="K12">
-        <v>17.63</v>
-      </c>
-      <c r="L12">
-        <v>-3.54</v>
-      </c>
-      <c r="M12">
-        <v>17.21</v>
-      </c>
-      <c r="N12">
-        <v>-3.95</v>
-      </c>
-      <c r="O12" s="1">
-        <v>17.190000000000001</v>
-      </c>
-      <c r="P12" s="1">
-        <v>-3.98</v>
-      </c>
-      <c r="Q12">
-        <v>17.23</v>
-      </c>
-      <c r="R12">
-        <v>-3.93</v>
-      </c>
-      <c r="S12">
-        <v>17.29</v>
-      </c>
-      <c r="T12">
-        <v>-3.88</v>
-      </c>
-      <c r="U12">
-        <v>16.95</v>
-      </c>
-      <c r="V12">
-        <v>-4.22</v>
-      </c>
-      <c r="W12">
-        <v>16.88</v>
-      </c>
-      <c r="X12">
-        <v>-4.28</v>
-      </c>
-      <c r="Y12">
-        <v>16.96</v>
-      </c>
-      <c r="Z12">
-        <v>-4.21</v>
-      </c>
       <c r="AA12">
-        <v>16.510000000000002</v>
+        <v>17.05</v>
       </c>
       <c r="AB12">
-        <v>-4.6500000000000004</v>
+        <v>-4.12</v>
       </c>
       <c r="AC12">
-        <v>19.12</v>
+        <v>19.079999999999998</v>
       </c>
       <c r="AD12">
-        <v>-2.0499999999999998</v>
+        <v>-2.08</v>
       </c>
       <c r="AE12">
-        <v>19.12</v>
+        <v>19.13</v>
       </c>
       <c r="AF12">
-        <v>-2.0499999999999998</v>
+        <v>-2.04</v>
       </c>
       <c r="AG12">
-        <v>18.93</v>
+        <v>18.82</v>
       </c>
       <c r="AH12">
-        <v>-2.2400000000000002</v>
+        <v>-2.35</v>
       </c>
       <c r="AI12">
-        <v>20.079999999999998</v>
+        <v>19.52</v>
       </c>
       <c r="AJ12">
-        <v>-1.0900000000000001</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B13">
         <v>14.7</v>
@@ -2545,105 +2597,105 @@
         <v>17</v>
       </c>
       <c r="E13">
-        <v>16.21</v>
+        <v>16.5</v>
       </c>
       <c r="F13">
-        <v>1.51</v>
+        <v>1.8</v>
       </c>
       <c r="G13" s="1">
+        <v>16.329999999999998</v>
+      </c>
+      <c r="H13" s="1">
+        <v>1.62</v>
+      </c>
+      <c r="I13">
+        <v>16.260000000000002</v>
+      </c>
+      <c r="J13">
+        <v>1.55</v>
+      </c>
+      <c r="K13">
+        <v>16.27</v>
+      </c>
+      <c r="L13">
+        <v>1.57</v>
+      </c>
+      <c r="M13">
+        <v>16.559999999999999</v>
+      </c>
+      <c r="N13">
+        <v>1.85</v>
+      </c>
+      <c r="O13">
+        <v>16.68</v>
+      </c>
+      <c r="P13">
+        <v>1.98</v>
+      </c>
+      <c r="Q13">
         <v>16.18</v>
       </c>
-      <c r="H13" s="1">
+      <c r="R13">
+        <v>1.48</v>
+      </c>
+      <c r="S13">
+        <v>16.43</v>
+      </c>
+      <c r="T13">
+        <v>1.73</v>
+      </c>
+      <c r="U13">
+        <v>16.72</v>
+      </c>
+      <c r="V13">
+        <v>2.02</v>
+      </c>
+      <c r="W13">
+        <v>16.18</v>
+      </c>
+      <c r="X13">
+        <v>1.48</v>
+      </c>
+      <c r="Y13">
+        <v>17.170000000000002</v>
+      </c>
+      <c r="Z13">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="AA13">
+        <v>16.170000000000002</v>
+      </c>
+      <c r="AB13">
         <v>1.47</v>
       </c>
-      <c r="I13">
-        <v>16.149999999999999</v>
-      </c>
-      <c r="J13">
-        <v>1.44</v>
-      </c>
-      <c r="K13">
-        <v>16.190000000000001</v>
-      </c>
-      <c r="L13">
-        <v>1.49</v>
-      </c>
-      <c r="M13">
-        <v>16.47</v>
-      </c>
-      <c r="N13">
-        <v>1.77</v>
-      </c>
-      <c r="O13" s="1">
-        <v>16.43</v>
-      </c>
-      <c r="P13" s="1">
-        <v>1.73</v>
-      </c>
-      <c r="Q13">
-        <v>16.21</v>
-      </c>
-      <c r="R13">
-        <v>1.51</v>
-      </c>
-      <c r="S13">
-        <v>16.25</v>
-      </c>
-      <c r="T13">
-        <v>1.55</v>
-      </c>
-      <c r="U13">
-        <v>16.399999999999999</v>
-      </c>
-      <c r="V13">
-        <v>1.69</v>
-      </c>
-      <c r="W13">
-        <v>16.399999999999999</v>
-      </c>
-      <c r="X13">
-        <v>1.7</v>
-      </c>
-      <c r="Y13">
-        <v>16.21</v>
-      </c>
-      <c r="Z13">
-        <v>1.51</v>
-      </c>
-      <c r="AA13">
-        <v>16.88</v>
-      </c>
-      <c r="AB13">
-        <v>2.1800000000000002</v>
-      </c>
       <c r="AC13">
-        <v>14.21</v>
+        <v>13.96</v>
       </c>
       <c r="AD13">
-        <v>-0.5</v>
+        <v>-0.74</v>
       </c>
       <c r="AE13">
-        <v>14.46</v>
+        <v>14.32</v>
       </c>
       <c r="AF13">
-        <v>-0.25</v>
+        <v>-0.39</v>
       </c>
       <c r="AG13">
-        <v>14.37</v>
+        <v>14.35</v>
       </c>
       <c r="AH13">
-        <v>-0.33</v>
+        <v>-0.35</v>
       </c>
       <c r="AI13">
-        <v>13.17</v>
+        <v>13.56</v>
       </c>
       <c r="AJ13">
-        <v>-1.53</v>
+        <v>-1.1399999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B14">
         <v>26.05</v>
@@ -2655,105 +2707,105 @@
         <v>27</v>
       </c>
       <c r="E14">
-        <v>26.33</v>
+        <v>26.26</v>
       </c>
       <c r="F14">
-        <v>0.28000000000000003</v>
+        <v>0.21</v>
       </c>
       <c r="G14" s="1">
-        <v>26.68</v>
+        <v>26.62</v>
       </c>
       <c r="H14" s="1">
-        <v>0.63</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="I14">
-        <v>26.18</v>
+        <v>26.04</v>
       </c>
       <c r="J14">
+        <v>-0.01</v>
+      </c>
+      <c r="K14">
+        <v>26.08</v>
+      </c>
+      <c r="L14">
+        <v>0.03</v>
+      </c>
+      <c r="M14">
+        <v>26.47</v>
+      </c>
+      <c r="N14">
+        <v>0.42</v>
+      </c>
+      <c r="O14">
+        <v>26.08</v>
+      </c>
+      <c r="P14">
+        <v>0.03</v>
+      </c>
+      <c r="Q14">
+        <v>26.37</v>
+      </c>
+      <c r="R14">
+        <v>0.32</v>
+      </c>
+      <c r="S14">
+        <v>26.45</v>
+      </c>
+      <c r="T14">
+        <v>0.4</v>
+      </c>
+      <c r="U14">
+        <v>26.11</v>
+      </c>
+      <c r="V14">
+        <v>0.06</v>
+      </c>
+      <c r="W14">
+        <v>26.43</v>
+      </c>
+      <c r="X14">
+        <v>0.38</v>
+      </c>
+      <c r="Y14">
+        <v>26.17</v>
+      </c>
+      <c r="Z14">
         <v>0.12</v>
       </c>
-      <c r="K14">
-        <v>26.27</v>
-      </c>
-      <c r="L14">
-        <v>0.21</v>
-      </c>
-      <c r="M14">
-        <v>26.13</v>
-      </c>
-      <c r="N14">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="O14" s="1">
-        <v>26.05</v>
-      </c>
-      <c r="P14" s="1">
-        <v>-0.01</v>
-      </c>
-      <c r="Q14">
-        <v>26.47</v>
-      </c>
-      <c r="R14">
-        <v>0.41</v>
-      </c>
-      <c r="S14">
+      <c r="AA14">
         <v>26.55</v>
       </c>
-      <c r="T14">
+      <c r="AB14">
         <v>0.5</v>
       </c>
-      <c r="U14">
-        <v>26.5</v>
-      </c>
-      <c r="V14">
-        <v>0.45</v>
-      </c>
-      <c r="W14">
-        <v>26.54</v>
-      </c>
-      <c r="X14">
-        <v>0.49</v>
-      </c>
-      <c r="Y14">
-        <v>26.64</v>
-      </c>
-      <c r="Z14">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="AA14">
-        <v>26.2</v>
-      </c>
-      <c r="AB14">
-        <v>0.15</v>
-      </c>
       <c r="AC14">
-        <v>25.51</v>
+        <v>25.44</v>
       </c>
       <c r="AD14">
-        <v>-0.54</v>
+        <v>-0.61</v>
       </c>
       <c r="AE14">
+        <v>23.92</v>
+      </c>
+      <c r="AF14">
+        <v>-2.13</v>
+      </c>
+      <c r="AG14">
+        <v>23.93</v>
+      </c>
+      <c r="AH14">
+        <v>-2.12</v>
+      </c>
+      <c r="AI14">
         <v>23.95</v>
       </c>
-      <c r="AF14">
-        <v>-2.1</v>
-      </c>
-      <c r="AG14">
-        <v>24.04</v>
-      </c>
-      <c r="AH14">
-        <v>-2.0099999999999998</v>
-      </c>
-      <c r="AI14">
-        <v>24.26</v>
-      </c>
       <c r="AJ14">
-        <v>-1.79</v>
+        <v>-2.11</v>
       </c>
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B15">
         <v>18.55</v>
@@ -2765,105 +2817,105 @@
         <v>20</v>
       </c>
       <c r="E15">
-        <v>19.53</v>
+        <v>19.36</v>
       </c>
       <c r="F15">
-        <v>0.98</v>
+        <v>0.82</v>
       </c>
       <c r="G15" s="1">
-        <v>18.989999999999998</v>
+        <v>18.84</v>
       </c>
       <c r="H15" s="1">
-        <v>0.44</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="I15">
-        <v>19.399999999999999</v>
+        <v>19.21</v>
       </c>
       <c r="J15">
-        <v>0.85</v>
+        <v>0.67</v>
       </c>
       <c r="K15">
-        <v>19.329999999999998</v>
+        <v>19.170000000000002</v>
       </c>
       <c r="L15">
-        <v>0.78</v>
+        <v>0.62</v>
       </c>
       <c r="M15">
-        <v>18.309999999999999</v>
+        <v>17.87</v>
       </c>
       <c r="N15">
-        <v>-0.23</v>
-      </c>
-      <c r="O15" s="1">
-        <v>18.32</v>
-      </c>
-      <c r="P15" s="1">
-        <v>-0.23</v>
+        <v>-0.67</v>
+      </c>
+      <c r="O15">
+        <v>17.89</v>
+      </c>
+      <c r="P15">
+        <v>-0.65</v>
       </c>
       <c r="Q15">
-        <v>17.600000000000001</v>
+        <v>17.239999999999998</v>
       </c>
       <c r="R15">
-        <v>-0.95</v>
+        <v>-1.3</v>
       </c>
       <c r="S15">
-        <v>17.62</v>
+        <v>17.079999999999998</v>
       </c>
       <c r="T15">
-        <v>-0.93</v>
+        <v>-1.46</v>
       </c>
       <c r="U15">
-        <v>18.23</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="V15">
-        <v>-0.31</v>
+        <v>-0.65</v>
       </c>
       <c r="W15">
-        <v>17.46</v>
+        <v>17.25</v>
       </c>
       <c r="X15">
-        <v>-1.0900000000000001</v>
+        <v>-1.3</v>
       </c>
       <c r="Y15">
-        <v>17.72</v>
+        <v>17.91</v>
       </c>
       <c r="Z15">
-        <v>-0.83</v>
+        <v>-0.64</v>
       </c>
       <c r="AA15">
-        <v>18.62</v>
+        <v>17.489999999999998</v>
       </c>
       <c r="AB15">
-        <v>7.0000000000000007E-2</v>
+        <v>-1.06</v>
       </c>
       <c r="AC15">
-        <v>18.59</v>
+        <v>18.54</v>
       </c>
       <c r="AD15">
-        <v>0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="AE15">
-        <v>19.239999999999998</v>
+        <v>19.12</v>
       </c>
       <c r="AF15">
-        <v>0.69</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="AG15">
-        <v>19.579999999999998</v>
+        <v>19.46</v>
       </c>
       <c r="AH15">
-        <v>1.03</v>
+        <v>0.92</v>
       </c>
       <c r="AI15">
-        <v>18.41</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="AJ15">
-        <v>-0.14000000000000001</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B16">
         <v>19.98</v>
@@ -2875,105 +2927,105 @@
         <v>20</v>
       </c>
       <c r="E16">
-        <v>20.84</v>
+        <v>20.46</v>
       </c>
       <c r="F16">
-        <v>0.87</v>
+        <v>0.48</v>
       </c>
       <c r="G16" s="1">
-        <v>20.27</v>
+        <v>19.86</v>
       </c>
       <c r="H16" s="1">
-        <v>0.28999999999999998</v>
+        <v>-0.11</v>
       </c>
       <c r="I16">
-        <v>20.68</v>
+        <v>20.190000000000001</v>
       </c>
       <c r="J16">
-        <v>0.71</v>
+        <v>0.22</v>
       </c>
       <c r="K16">
-        <v>20.69</v>
+        <v>20.239999999999998</v>
       </c>
       <c r="L16">
-        <v>0.72</v>
+        <v>0.26</v>
       </c>
       <c r="M16">
-        <v>21.62</v>
+        <v>20.64</v>
       </c>
       <c r="N16">
-        <v>1.64</v>
-      </c>
-      <c r="O16" s="1">
-        <v>21.59</v>
-      </c>
-      <c r="P16" s="1">
-        <v>1.61</v>
+        <v>0.67</v>
+      </c>
+      <c r="O16">
+        <v>21.18</v>
+      </c>
+      <c r="P16">
+        <v>1.21</v>
       </c>
       <c r="Q16">
-        <v>21.57</v>
+        <v>21.26</v>
       </c>
       <c r="R16">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="S16">
-        <v>21.57</v>
+        <v>21.45</v>
       </c>
       <c r="T16">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="U16">
-        <v>20.94</v>
+        <v>21.18</v>
       </c>
       <c r="V16">
-        <v>0.97</v>
+        <v>1.2</v>
       </c>
       <c r="W16">
-        <v>21.72</v>
+        <v>21.25</v>
       </c>
       <c r="X16">
-        <v>1.74</v>
+        <v>1.27</v>
       </c>
       <c r="Y16">
-        <v>21.23</v>
+        <v>21.12</v>
       </c>
       <c r="Z16">
-        <v>1.26</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="AA16">
-        <v>21.25</v>
+        <v>20.87</v>
       </c>
       <c r="AB16">
-        <v>1.28</v>
+        <v>0.89</v>
       </c>
       <c r="AC16">
-        <v>17.57</v>
+        <v>17.489999999999998</v>
       </c>
       <c r="AD16">
-        <v>-2.41</v>
+        <v>-2.4900000000000002</v>
       </c>
       <c r="AE16">
-        <v>18.12</v>
+        <v>18</v>
       </c>
       <c r="AF16">
-        <v>-1.86</v>
+        <v>-1.97</v>
       </c>
       <c r="AG16">
-        <v>18.36</v>
+        <v>18.28</v>
       </c>
       <c r="AH16">
-        <v>-1.61</v>
+        <v>-1.7</v>
       </c>
       <c r="AI16">
-        <v>17.13</v>
+        <v>17.010000000000002</v>
       </c>
       <c r="AJ16">
-        <v>-2.84</v>
+        <v>-2.96</v>
       </c>
     </row>
     <row r="17" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B17">
         <v>7.92</v>
@@ -2985,76 +3037,76 @@
         <v>7</v>
       </c>
       <c r="E17">
-        <v>7.6</v>
+        <v>7.63</v>
       </c>
       <c r="F17">
+        <v>-0.3</v>
+      </c>
+      <c r="G17" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="H17" s="1">
+        <v>-0.42</v>
+      </c>
+      <c r="I17">
+        <v>7.67</v>
+      </c>
+      <c r="J17">
+        <v>-0.25</v>
+      </c>
+      <c r="K17">
+        <v>7.84</v>
+      </c>
+      <c r="L17">
+        <v>-0.09</v>
+      </c>
+      <c r="M17">
+        <v>7.34</v>
+      </c>
+      <c r="N17">
+        <v>-0.57999999999999996</v>
+      </c>
+      <c r="O17">
+        <v>7.36</v>
+      </c>
+      <c r="P17">
+        <v>-0.56000000000000005</v>
+      </c>
+      <c r="Q17">
+        <v>7.49</v>
+      </c>
+      <c r="R17">
+        <v>-0.43</v>
+      </c>
+      <c r="S17">
+        <v>7.54</v>
+      </c>
+      <c r="T17">
+        <v>-0.38</v>
+      </c>
+      <c r="U17">
+        <v>7.59</v>
+      </c>
+      <c r="V17">
         <v>-0.33</v>
       </c>
-      <c r="G17" s="1">
-        <v>7.47</v>
-      </c>
-      <c r="H17" s="1">
-        <v>-0.45</v>
-      </c>
-      <c r="I17">
-        <v>7.65</v>
-      </c>
-      <c r="J17">
-        <v>-0.27</v>
-      </c>
-      <c r="K17">
-        <v>7.76</v>
-      </c>
-      <c r="L17">
-        <v>-0.17</v>
-      </c>
-      <c r="M17">
-        <v>7.57</v>
-      </c>
-      <c r="N17">
-        <v>-0.36</v>
-      </c>
-      <c r="O17" s="1">
-        <v>7.39</v>
-      </c>
-      <c r="P17" s="1">
-        <v>-0.53</v>
-      </c>
-      <c r="Q17">
-        <v>7.45</v>
-      </c>
-      <c r="R17">
-        <v>-0.47</v>
-      </c>
-      <c r="S17">
-        <v>7.56</v>
-      </c>
-      <c r="T17">
-        <v>-0.36</v>
-      </c>
-      <c r="U17">
-        <v>7.32</v>
-      </c>
-      <c r="V17">
-        <v>-0.6</v>
-      </c>
       <c r="W17">
-        <v>7.46</v>
+        <v>7.69</v>
       </c>
       <c r="X17">
-        <v>-0.46</v>
+        <v>-0.24</v>
       </c>
       <c r="Y17">
         <v>7.35</v>
       </c>
       <c r="Z17">
-        <v>-0.57999999999999996</v>
+        <v>-0.56999999999999995</v>
       </c>
       <c r="AA17">
-        <v>7.26</v>
+        <v>7.36</v>
       </c>
       <c r="AB17">
-        <v>-0.67</v>
+        <v>-0.56999999999999995</v>
       </c>
       <c r="AC17">
         <v>7.44</v>
@@ -3063,132 +3115,84 @@
         <v>-0.49</v>
       </c>
       <c r="AE17">
-        <v>6.89</v>
+        <v>6.75</v>
       </c>
       <c r="AF17">
-        <v>-1.03</v>
+        <v>-1.17</v>
       </c>
       <c r="AG17">
-        <v>6.87</v>
+        <v>6.84</v>
       </c>
       <c r="AH17">
-        <v>-1.05</v>
+        <v>-1.08</v>
       </c>
       <c r="AI17">
-        <v>7.39</v>
+        <v>7.08</v>
       </c>
       <c r="AJ17">
-        <v>-0.53</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="18" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" t="s">
         <v>52</v>
       </c>
-      <c r="B18">
-        <v>20.149999999999999</v>
-      </c>
-      <c r="C18">
-        <v>18</v>
+      <c r="C18" t="s">
+        <v>52</v>
       </c>
       <c r="D18">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="E18">
-        <v>21.79</v>
-      </c>
-      <c r="F18">
-        <v>1.64</v>
+        <v>4.76</v>
       </c>
       <c r="G18" s="1">
-        <v>21.42</v>
-      </c>
-      <c r="H18" s="1">
-        <v>1.26</v>
+        <v>5</v>
       </c>
       <c r="I18">
-        <v>21.72</v>
-      </c>
-      <c r="J18">
-        <v>1.57</v>
+        <v>5.14</v>
       </c>
       <c r="K18">
-        <v>21.63</v>
-      </c>
-      <c r="L18">
-        <v>1.48</v>
+        <v>5.15</v>
       </c>
       <c r="M18">
-        <v>21.67</v>
-      </c>
-      <c r="N18">
-        <v>1.52</v>
-      </c>
-      <c r="O18" s="1">
-        <v>21.77</v>
-      </c>
-      <c r="P18" s="1">
-        <v>1.61</v>
+        <v>6.05</v>
+      </c>
+      <c r="O18">
+        <v>6.19</v>
       </c>
       <c r="Q18">
-        <v>21.72</v>
-      </c>
-      <c r="R18">
-        <v>1.56</v>
+        <v>5.59</v>
       </c>
       <c r="S18">
-        <v>21.59</v>
-      </c>
-      <c r="T18">
-        <v>1.44</v>
+        <v>5.35</v>
       </c>
       <c r="U18">
-        <v>21.51</v>
-      </c>
-      <c r="V18">
-        <v>1.36</v>
+        <v>6.15</v>
       </c>
       <c r="W18">
-        <v>21.83</v>
-      </c>
-      <c r="X18">
-        <v>1.68</v>
+        <v>5.59</v>
       </c>
       <c r="Y18">
-        <v>21.54</v>
-      </c>
-      <c r="Z18">
-        <v>1.39</v>
+        <v>6.06</v>
       </c>
       <c r="AA18">
-        <v>21.94</v>
-      </c>
-      <c r="AB18">
-        <v>1.79</v>
+        <v>5.58</v>
       </c>
       <c r="AC18">
-        <v>22.45</v>
-      </c>
-      <c r="AD18">
-        <v>2.2999999999999998</v>
+        <v>6.29</v>
       </c>
       <c r="AE18">
-        <v>23.63</v>
-      </c>
-      <c r="AF18">
-        <v>3.47</v>
+        <v>6.34</v>
       </c>
       <c r="AG18">
-        <v>23.43</v>
-      </c>
-      <c r="AH18">
-        <v>3.27</v>
+        <v>6.22</v>
       </c>
       <c r="AI18">
-        <v>23.49</v>
-      </c>
-      <c r="AJ18">
-        <v>3.34</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="19" spans="1:36" x14ac:dyDescent="0.25">
@@ -3196,109 +3200,109 @@
         <v>53</v>
       </c>
       <c r="B19">
-        <v>6.51</v>
+        <v>20.149999999999999</v>
       </c>
       <c r="C19">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D19">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E19">
-        <v>6.28</v>
+        <v>21.91</v>
       </c>
       <c r="F19">
-        <v>-0.23</v>
+        <v>1.75</v>
       </c>
       <c r="G19" s="1">
-        <v>6.43</v>
+        <v>21.55</v>
       </c>
       <c r="H19" s="1">
-        <v>-0.08</v>
+        <v>1.39</v>
       </c>
       <c r="I19">
-        <v>6.58</v>
+        <v>21.99</v>
       </c>
       <c r="J19">
-        <v>7.0000000000000007E-2</v>
+        <v>1.83</v>
       </c>
       <c r="K19">
-        <v>6.61</v>
+        <v>21.87</v>
       </c>
       <c r="L19">
-        <v>0.1</v>
+        <v>1.72</v>
       </c>
       <c r="M19">
-        <v>7.16</v>
+        <v>21.59</v>
       </c>
       <c r="N19">
-        <v>0.65</v>
-      </c>
-      <c r="O19" s="1">
-        <v>7.18</v>
-      </c>
-      <c r="P19" s="1">
-        <v>0.67</v>
+        <v>1.44</v>
+      </c>
+      <c r="O19">
+        <v>21.92</v>
+      </c>
+      <c r="P19">
+        <v>1.76</v>
       </c>
       <c r="Q19">
-        <v>7.07</v>
+        <v>21.93</v>
       </c>
       <c r="R19">
-        <v>0.56000000000000005</v>
+        <v>1.77</v>
       </c>
       <c r="S19">
-        <v>7.08</v>
+        <v>21.87</v>
       </c>
       <c r="T19">
-        <v>0.56999999999999995</v>
+        <v>1.72</v>
       </c>
       <c r="U19">
-        <v>7.09</v>
+        <v>21.79</v>
       </c>
       <c r="V19">
-        <v>0.57999999999999996</v>
+        <v>1.64</v>
       </c>
       <c r="W19">
-        <v>6.96</v>
+        <v>21.78</v>
       </c>
       <c r="X19">
-        <v>0.45</v>
+        <v>1.63</v>
       </c>
       <c r="Y19">
-        <v>7.06</v>
+        <v>21.86</v>
       </c>
       <c r="Z19">
-        <v>0.55000000000000004</v>
+        <v>1.7</v>
       </c>
       <c r="AA19">
-        <v>7.18</v>
+        <v>21.66</v>
       </c>
       <c r="AB19">
-        <v>0.67</v>
+        <v>1.51</v>
       </c>
       <c r="AC19">
-        <v>7.89</v>
+        <v>22.58</v>
       </c>
       <c r="AD19">
-        <v>1.38</v>
+        <v>2.4300000000000002</v>
       </c>
       <c r="AE19">
-        <v>7.71</v>
+        <v>23.72</v>
       </c>
       <c r="AF19">
-        <v>1.2</v>
+        <v>3.57</v>
       </c>
       <c r="AG19">
-        <v>7.54</v>
+        <v>23.55</v>
       </c>
       <c r="AH19">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AI19">
-        <v>7.41</v>
+        <v>23.92</v>
       </c>
       <c r="AJ19">
-        <v>0.9</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="20" spans="1:36" x14ac:dyDescent="0.25">
@@ -3306,109 +3310,109 @@
         <v>54</v>
       </c>
       <c r="B20">
-        <v>8.06</v>
+        <v>6.51</v>
       </c>
       <c r="C20">
+        <v>7</v>
+      </c>
+      <c r="D20">
         <v>9</v>
       </c>
-      <c r="D20">
+      <c r="E20">
+        <v>6.32</v>
+      </c>
+      <c r="F20">
+        <v>-0.19</v>
+      </c>
+      <c r="G20" s="1">
+        <v>6.66</v>
+      </c>
+      <c r="H20" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="I20">
+        <v>6.78</v>
+      </c>
+      <c r="J20">
+        <v>0.27</v>
+      </c>
+      <c r="K20">
+        <v>6.8</v>
+      </c>
+      <c r="L20">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="M20">
+        <v>7.51</v>
+      </c>
+      <c r="N20">
+        <v>1</v>
+      </c>
+      <c r="O20">
+        <v>7.54</v>
+      </c>
+      <c r="P20">
+        <v>1.03</v>
+      </c>
+      <c r="Q20">
+        <v>7.34</v>
+      </c>
+      <c r="R20">
+        <v>0.83</v>
+      </c>
+      <c r="S20">
+        <v>7.13</v>
+      </c>
+      <c r="T20">
+        <v>0.62</v>
+      </c>
+      <c r="U20">
+        <v>7.52</v>
+      </c>
+      <c r="V20">
+        <v>1.01</v>
+      </c>
+      <c r="W20">
+        <v>7.35</v>
+      </c>
+      <c r="X20">
+        <v>0.84</v>
+      </c>
+      <c r="Y20">
+        <v>7.42</v>
+      </c>
+      <c r="Z20">
+        <v>0.91</v>
+      </c>
+      <c r="AA20">
+        <v>7.35</v>
+      </c>
+      <c r="AB20">
+        <v>0.84</v>
+      </c>
+      <c r="AC20">
         <v>7</v>
       </c>
-      <c r="E20">
-        <v>7.9</v>
-      </c>
-      <c r="F20">
-        <v>-0.17</v>
-      </c>
-      <c r="G20" s="1">
-        <v>7.71</v>
-      </c>
-      <c r="H20" s="1">
-        <v>-0.35</v>
-      </c>
-      <c r="I20">
-        <v>8.1</v>
-      </c>
-      <c r="J20">
-        <v>0.04</v>
-      </c>
-      <c r="K20">
-        <v>8.26</v>
-      </c>
-      <c r="L20">
-        <v>0.19</v>
-      </c>
-      <c r="M20">
-        <v>7.95</v>
-      </c>
-      <c r="N20">
-        <v>-0.11</v>
-      </c>
-      <c r="O20" s="1">
-        <v>7.79</v>
-      </c>
-      <c r="P20" s="1">
-        <v>-0.27</v>
-      </c>
-      <c r="Q20">
-        <v>7.82</v>
-      </c>
-      <c r="R20">
-        <v>-0.24</v>
-      </c>
-      <c r="S20">
-        <v>7.98</v>
-      </c>
-      <c r="T20">
-        <v>-0.09</v>
-      </c>
-      <c r="U20">
-        <v>7.65</v>
-      </c>
-      <c r="V20">
-        <v>-0.41</v>
-      </c>
-      <c r="W20">
-        <v>7.81</v>
-      </c>
-      <c r="X20">
-        <v>-0.25</v>
-      </c>
-      <c r="Y20">
-        <v>7.68</v>
-      </c>
-      <c r="Z20">
-        <v>-0.39</v>
-      </c>
-      <c r="AA20">
-        <v>7.75</v>
-      </c>
-      <c r="AB20">
-        <v>-0.31</v>
-      </c>
-      <c r="AC20">
+      <c r="AD20">
+        <v>0.49</v>
+      </c>
+      <c r="AE20">
+        <v>7.09</v>
+      </c>
+      <c r="AF20">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="AG20">
+        <v>6.94</v>
+      </c>
+      <c r="AH20">
+        <v>0.43</v>
+      </c>
+      <c r="AI20">
         <v>7.12</v>
       </c>
-      <c r="AD20">
-        <v>-0.94</v>
-      </c>
-      <c r="AE20">
-        <v>6.78</v>
-      </c>
-      <c r="AF20">
-        <v>-1.28</v>
-      </c>
-      <c r="AG20">
-        <v>6.76</v>
-      </c>
-      <c r="AH20">
-        <v>-1.3</v>
-      </c>
-      <c r="AI20">
-        <v>7.03</v>
-      </c>
       <c r="AJ20">
-        <v>-1.04</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="21" spans="1:36" x14ac:dyDescent="0.25">
@@ -3416,109 +3420,109 @@
         <v>55</v>
       </c>
       <c r="B21">
-        <v>11.14</v>
+        <v>8.06</v>
       </c>
       <c r="C21">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D21">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E21">
-        <v>11.01</v>
+        <v>7.91</v>
       </c>
       <c r="F21">
-        <v>-0.13</v>
+        <v>-0.15</v>
       </c>
       <c r="G21" s="1">
-        <v>10.91</v>
+        <v>7.71</v>
       </c>
       <c r="H21" s="1">
-        <v>-0.22</v>
+        <v>-0.35</v>
       </c>
       <c r="I21">
-        <v>10.3</v>
+        <v>8.1</v>
       </c>
       <c r="J21">
-        <v>-0.83</v>
+        <v>0.04</v>
       </c>
       <c r="K21">
-        <v>10.17</v>
+        <v>8.24</v>
       </c>
       <c r="L21">
-        <v>-0.96</v>
+        <v>0.18</v>
       </c>
       <c r="M21">
-        <v>10.02</v>
+        <v>7.61</v>
       </c>
       <c r="N21">
-        <v>-1.1200000000000001</v>
-      </c>
-      <c r="O21" s="1">
-        <v>10.220000000000001</v>
-      </c>
-      <c r="P21" s="1">
-        <v>-0.92</v>
+        <v>-0.45</v>
+      </c>
+      <c r="O21">
+        <v>7.68</v>
+      </c>
+      <c r="P21">
+        <v>-0.38</v>
       </c>
       <c r="Q21">
-        <v>10.199999999999999</v>
+        <v>7.82</v>
       </c>
       <c r="R21">
-        <v>-0.93</v>
+        <v>-0.24</v>
       </c>
       <c r="S21">
-        <v>9.9600000000000009</v>
+        <v>7.8</v>
       </c>
       <c r="T21">
-        <v>-1.17</v>
+        <v>-0.26</v>
       </c>
       <c r="U21">
-        <v>10.29</v>
+        <v>7.84</v>
       </c>
       <c r="V21">
-        <v>-0.84</v>
+        <v>-0.23</v>
       </c>
       <c r="W21">
-        <v>10.47</v>
+        <v>7.98</v>
       </c>
       <c r="X21">
-        <v>-0.67</v>
+        <v>-0.08</v>
       </c>
       <c r="Y21">
-        <v>10.210000000000001</v>
+        <v>7.71</v>
       </c>
       <c r="Z21">
-        <v>-0.92</v>
+        <v>-0.35</v>
       </c>
       <c r="AA21">
-        <v>10.73</v>
+        <v>7.61</v>
       </c>
       <c r="AB21">
-        <v>-0.4</v>
+        <v>-0.45</v>
       </c>
       <c r="AC21">
-        <v>7.09</v>
+        <v>7.05</v>
       </c>
       <c r="AD21">
-        <v>-4.05</v>
+        <v>-1.01</v>
       </c>
       <c r="AE21">
-        <v>9.77</v>
+        <v>6.12</v>
       </c>
       <c r="AF21">
-        <v>-1.37</v>
+        <v>-1.95</v>
       </c>
       <c r="AG21">
-        <v>9.9499999999999993</v>
+        <v>6.03</v>
       </c>
       <c r="AH21">
-        <v>-1.19</v>
+        <v>-2.04</v>
       </c>
       <c r="AI21">
-        <v>6.99</v>
+        <v>6.31</v>
       </c>
       <c r="AJ21">
-        <v>-4.1399999999999997</v>
+        <v>-1.76</v>
       </c>
     </row>
     <row r="22" spans="1:36" x14ac:dyDescent="0.25">
@@ -3526,109 +3530,109 @@
         <v>56</v>
       </c>
       <c r="B22">
-        <v>16.440000000000001</v>
+        <v>11.14</v>
       </c>
       <c r="C22">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D22">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E22">
-        <v>17.03</v>
+        <v>10.53</v>
       </c>
       <c r="F22">
-        <v>0.6</v>
+        <v>-0.61</v>
       </c>
       <c r="G22" s="1">
-        <v>17.63</v>
+        <v>10.41</v>
       </c>
       <c r="H22" s="1">
-        <v>1.2</v>
+        <v>-0.72</v>
       </c>
       <c r="I22">
-        <v>16.989999999999998</v>
+        <v>9.9700000000000006</v>
       </c>
       <c r="J22">
-        <v>0.56000000000000005</v>
+        <v>-1.17</v>
       </c>
       <c r="K22">
-        <v>16.98</v>
+        <v>9.7100000000000009</v>
       </c>
       <c r="L22">
-        <v>0.54</v>
+        <v>-1.43</v>
       </c>
       <c r="M22">
-        <v>19.07</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="N22">
-        <v>2.64</v>
-      </c>
-      <c r="O22" s="1">
-        <v>19.170000000000002</v>
-      </c>
-      <c r="P22" s="1">
-        <v>2.73</v>
+        <v>-1.43</v>
+      </c>
+      <c r="O22">
+        <v>9.86</v>
+      </c>
+      <c r="P22">
+        <v>-1.28</v>
       </c>
       <c r="Q22">
-        <v>19.52</v>
+        <v>9.81</v>
       </c>
       <c r="R22">
-        <v>3.09</v>
+        <v>-1.32</v>
       </c>
       <c r="S22">
-        <v>19.440000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="T22">
-        <v>3</v>
+        <v>-1.23</v>
       </c>
       <c r="U22">
-        <v>19.940000000000001</v>
+        <v>9.5399999999999991</v>
       </c>
       <c r="V22">
-        <v>3.5</v>
+        <v>-1.59</v>
       </c>
       <c r="W22">
-        <v>19.79</v>
+        <v>9.4600000000000009</v>
       </c>
       <c r="X22">
-        <v>3.36</v>
+        <v>-1.68</v>
       </c>
       <c r="Y22">
-        <v>20</v>
+        <v>9.9700000000000006</v>
       </c>
       <c r="Z22">
-        <v>3.56</v>
+        <v>-1.1599999999999999</v>
       </c>
       <c r="AA22">
-        <v>20.13</v>
+        <v>9.69</v>
       </c>
       <c r="AB22">
-        <v>3.7</v>
+        <v>-1.44</v>
       </c>
       <c r="AC22">
-        <v>16.07</v>
+        <v>7.01</v>
       </c>
       <c r="AD22">
-        <v>-0.37</v>
+        <v>-4.13</v>
       </c>
       <c r="AE22">
-        <v>17.82</v>
+        <v>9.65</v>
       </c>
       <c r="AF22">
-        <v>1.38</v>
+        <v>-1.48</v>
       </c>
       <c r="AG22">
-        <v>18.03</v>
+        <v>9.89</v>
       </c>
       <c r="AH22">
-        <v>1.59</v>
+        <v>-1.25</v>
       </c>
       <c r="AI22">
-        <v>17.05</v>
+        <v>6.22</v>
       </c>
       <c r="AJ22">
-        <v>0.61</v>
+        <v>-4.92</v>
       </c>
     </row>
     <row r="23" spans="1:36" x14ac:dyDescent="0.25">
@@ -3636,109 +3640,109 @@
         <v>57</v>
       </c>
       <c r="B23">
-        <v>5</v>
+        <v>16.440000000000001</v>
       </c>
       <c r="C23">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D23">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="E23">
-        <v>5.36</v>
+        <v>16.87</v>
       </c>
       <c r="F23">
-        <v>0.37</v>
+        <v>0.43</v>
       </c>
       <c r="G23" s="1">
-        <v>5.59</v>
+        <v>17.23</v>
       </c>
       <c r="H23" s="1">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="I23">
-        <v>5.43</v>
+        <v>16.809999999999999</v>
       </c>
       <c r="J23">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="K23">
-        <v>5.46</v>
+        <v>16.829999999999998</v>
       </c>
       <c r="L23">
-        <v>0.47</v>
+        <v>0.39</v>
       </c>
       <c r="M23">
-        <v>5.55</v>
+        <v>19.62</v>
       </c>
       <c r="N23">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="O23" s="1">
-        <v>5.54</v>
-      </c>
-      <c r="P23" s="1">
-        <v>0.54</v>
+        <v>3.19</v>
+      </c>
+      <c r="O23">
+        <v>19.04</v>
+      </c>
+      <c r="P23">
+        <v>2.61</v>
       </c>
       <c r="Q23">
-        <v>5.46</v>
+        <v>19.38</v>
       </c>
       <c r="R23">
-        <v>0.47</v>
+        <v>2.94</v>
       </c>
       <c r="S23">
-        <v>5.51</v>
+        <v>19.59</v>
       </c>
       <c r="T23">
-        <v>0.51</v>
+        <v>3.15</v>
       </c>
       <c r="U23">
-        <v>5.68</v>
+        <v>19.02</v>
       </c>
       <c r="V23">
-        <v>0.69</v>
+        <v>2.59</v>
       </c>
       <c r="W23">
-        <v>5.47</v>
+        <v>19.29</v>
       </c>
       <c r="X23">
-        <v>0.47</v>
+        <v>2.86</v>
       </c>
       <c r="Y23">
-        <v>5.64</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="Z23">
-        <v>0.65</v>
+        <v>2.97</v>
       </c>
       <c r="AA23">
-        <v>5.72</v>
+        <v>19.850000000000001</v>
       </c>
       <c r="AB23">
-        <v>0.72</v>
+        <v>3.42</v>
       </c>
       <c r="AC23">
-        <v>6.56</v>
+        <v>16.11</v>
       </c>
       <c r="AD23">
-        <v>1.57</v>
+        <v>-0.32</v>
       </c>
       <c r="AE23">
-        <v>6.33</v>
+        <v>17.77</v>
       </c>
       <c r="AF23">
         <v>1.33</v>
       </c>
       <c r="AG23">
-        <v>6.41</v>
+        <v>17.989999999999998</v>
       </c>
       <c r="AH23">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="AI23">
-        <v>6.82</v>
+        <v>16.940000000000001</v>
       </c>
       <c r="AJ23">
-        <v>1.83</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="24" spans="1:36" x14ac:dyDescent="0.25">
@@ -3746,109 +3750,109 @@
         <v>58</v>
       </c>
       <c r="B24">
-        <v>7.83</v>
+        <v>5</v>
       </c>
       <c r="C24">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D24">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E24">
-        <v>7.25</v>
+        <v>5.55</v>
       </c>
       <c r="F24">
-        <v>-0.57999999999999996</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="G24" s="1">
-        <v>7.03</v>
+        <v>5.8</v>
       </c>
       <c r="H24" s="1">
-        <v>-0.8</v>
+        <v>0.8</v>
       </c>
       <c r="I24">
-        <v>7.5</v>
+        <v>5.77</v>
       </c>
       <c r="J24">
-        <v>-0.33</v>
+        <v>0.78</v>
       </c>
       <c r="K24">
-        <v>7.59</v>
+        <v>5.81</v>
       </c>
       <c r="L24">
-        <v>-0.24</v>
+        <v>0.81</v>
       </c>
       <c r="M24">
-        <v>7.75</v>
+        <v>6.01</v>
       </c>
       <c r="N24">
-        <v>-0.08</v>
-      </c>
-      <c r="O24" s="1">
-        <v>7.66</v>
-      </c>
-      <c r="P24" s="1">
-        <v>-0.17</v>
+        <v>1.02</v>
+      </c>
+      <c r="O24">
+        <v>5.89</v>
+      </c>
+      <c r="P24">
+        <v>0.89</v>
       </c>
       <c r="Q24">
-        <v>7.61</v>
+        <v>5.9</v>
       </c>
       <c r="R24">
-        <v>-0.22</v>
+        <v>0.9</v>
       </c>
       <c r="S24">
-        <v>7.69</v>
+        <v>5.82</v>
       </c>
       <c r="T24">
-        <v>-0.14000000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="U24">
-        <v>7.49</v>
+        <v>5.92</v>
       </c>
       <c r="V24">
-        <v>-0.35</v>
+        <v>0.93</v>
       </c>
       <c r="W24">
-        <v>7.5</v>
+        <v>5.94</v>
       </c>
       <c r="X24">
-        <v>-0.33</v>
+        <v>0.95</v>
       </c>
       <c r="Y24">
-        <v>7.48</v>
+        <v>5.86</v>
       </c>
       <c r="Z24">
-        <v>-0.36</v>
+        <v>0.86</v>
       </c>
       <c r="AA24">
-        <v>7.6</v>
+        <v>6.04</v>
       </c>
       <c r="AB24">
-        <v>-0.23</v>
+        <v>1.04</v>
       </c>
       <c r="AC24">
-        <v>7.5</v>
+        <v>5.36</v>
       </c>
       <c r="AD24">
-        <v>-0.33</v>
+        <v>0.36</v>
       </c>
       <c r="AE24">
-        <v>7.43</v>
+        <v>5.37</v>
       </c>
       <c r="AF24">
-        <v>-0.4</v>
+        <v>0.37</v>
       </c>
       <c r="AG24">
-        <v>7.21</v>
+        <v>5.32</v>
       </c>
       <c r="AH24">
-        <v>-0.62</v>
+        <v>0.33</v>
       </c>
       <c r="AI24">
-        <v>7.46</v>
+        <v>5.6</v>
       </c>
       <c r="AJ24">
-        <v>-0.37</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="25" spans="1:36" x14ac:dyDescent="0.25">
@@ -3856,109 +3860,109 @@
         <v>59</v>
       </c>
       <c r="B25">
-        <v>5.89</v>
+        <v>7.83</v>
       </c>
       <c r="C25">
+        <v>8</v>
+      </c>
+      <c r="D25">
         <v>7</v>
       </c>
-      <c r="D25">
-        <v>8</v>
-      </c>
       <c r="E25">
-        <v>6.24</v>
+        <v>7.11</v>
       </c>
       <c r="F25">
-        <v>0.35</v>
+        <v>-0.73</v>
       </c>
       <c r="G25" s="1">
-        <v>5.86</v>
+        <v>6.92</v>
       </c>
       <c r="H25" s="1">
-        <v>-0.03</v>
+        <v>-0.92</v>
       </c>
       <c r="I25">
-        <v>6.1</v>
+        <v>7.41</v>
       </c>
       <c r="J25">
-        <v>0.21</v>
+        <v>-0.42</v>
       </c>
       <c r="K25">
-        <v>6.14</v>
+        <v>7.54</v>
       </c>
       <c r="L25">
-        <v>0.25</v>
+        <v>-0.28999999999999998</v>
       </c>
       <c r="M25">
-        <v>6.21</v>
+        <v>7.49</v>
       </c>
       <c r="N25">
-        <v>0.32</v>
-      </c>
-      <c r="O25" s="1">
-        <v>6.21</v>
-      </c>
-      <c r="P25" s="1">
-        <v>0.32</v>
+        <v>-0.35</v>
+      </c>
+      <c r="O25">
+        <v>7.57</v>
+      </c>
+      <c r="P25">
+        <v>-0.27</v>
       </c>
       <c r="Q25">
-        <v>6.12</v>
+        <v>7.63</v>
       </c>
       <c r="R25">
-        <v>0.23</v>
+        <v>-0.21</v>
       </c>
       <c r="S25">
-        <v>6.09</v>
+        <v>7.5</v>
       </c>
       <c r="T25">
-        <v>0.2</v>
+        <v>-0.34</v>
       </c>
       <c r="U25">
-        <v>6.06</v>
+        <v>7.69</v>
       </c>
       <c r="V25">
-        <v>0.18</v>
+        <v>-0.14000000000000001</v>
       </c>
       <c r="W25">
-        <v>6.16</v>
+        <v>7.75</v>
       </c>
       <c r="X25">
-        <v>0.27</v>
+        <v>-0.08</v>
       </c>
       <c r="Y25">
-        <v>6.01</v>
+        <v>7.46</v>
       </c>
       <c r="Z25">
-        <v>0.12</v>
+        <v>-0.38</v>
       </c>
       <c r="AA25">
-        <v>6.41</v>
+        <v>7.45</v>
       </c>
       <c r="AB25">
-        <v>0.52</v>
+        <v>-0.38</v>
       </c>
       <c r="AC25">
-        <v>6.9</v>
+        <v>7.51</v>
       </c>
       <c r="AD25">
-        <v>1.01</v>
+        <v>-0.32</v>
       </c>
       <c r="AE25">
-        <v>6.46</v>
+        <v>7.05</v>
       </c>
       <c r="AF25">
-        <v>0.56999999999999995</v>
+        <v>-0.78</v>
       </c>
       <c r="AG25">
-        <v>7.03</v>
+        <v>6.88</v>
       </c>
       <c r="AH25">
-        <v>1.1399999999999999</v>
+        <v>-0.95</v>
       </c>
       <c r="AI25">
-        <v>6.79</v>
+        <v>7.21</v>
       </c>
       <c r="AJ25">
-        <v>0.9</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="26" spans="1:36" x14ac:dyDescent="0.25">
@@ -3966,7 +3970,7 @@
         <v>60</v>
       </c>
       <c r="B26">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="C26">
         <v>4</v>
@@ -3975,100 +3979,100 @@
         <v>4</v>
       </c>
       <c r="E26">
-        <v>4.2699999999999996</v>
+        <v>5.2</v>
       </c>
       <c r="F26">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="G26" s="1">
-        <v>4.45</v>
+        <v>5.31</v>
       </c>
       <c r="H26" s="1">
-        <v>1.45</v>
+        <v>1.71</v>
       </c>
       <c r="I26">
-        <v>4</v>
+        <v>5.21</v>
       </c>
       <c r="J26">
-        <v>1</v>
+        <v>1.61</v>
       </c>
       <c r="K26">
-        <v>3.97</v>
+        <v>5.21</v>
       </c>
       <c r="L26">
-        <v>0.97</v>
+        <v>1.61</v>
       </c>
       <c r="M26">
-        <v>5.2</v>
+        <v>5.49</v>
       </c>
       <c r="N26">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="O26" s="1">
-        <v>5.21</v>
-      </c>
-      <c r="P26" s="1">
-        <v>2.21</v>
+        <v>1.89</v>
+      </c>
+      <c r="O26">
+        <v>5.44</v>
+      </c>
+      <c r="P26">
+        <v>1.84</v>
       </c>
       <c r="Q26">
-        <v>5.46</v>
+        <v>5.33</v>
       </c>
       <c r="R26">
-        <v>2.46</v>
+        <v>1.73</v>
       </c>
       <c r="S26">
-        <v>5.47</v>
+        <v>5.35</v>
       </c>
       <c r="T26">
-        <v>2.4700000000000002</v>
+        <v>1.75</v>
       </c>
       <c r="U26">
-        <v>5.01</v>
+        <v>5.43</v>
       </c>
       <c r="V26">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="W26">
-        <v>5.21</v>
+        <v>5.33</v>
       </c>
       <c r="X26">
-        <v>2.21</v>
+        <v>1.73</v>
       </c>
       <c r="Y26">
-        <v>5.21</v>
+        <v>5.54</v>
       </c>
       <c r="Z26">
-        <v>2.21</v>
+        <v>1.94</v>
       </c>
       <c r="AA26">
-        <v>4.7699999999999996</v>
+        <v>5.4</v>
       </c>
       <c r="AB26">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AC26">
-        <v>6.35</v>
+        <v>4.97</v>
       </c>
       <c r="AD26">
-        <v>3.35</v>
+        <v>1.37</v>
       </c>
       <c r="AE26">
-        <v>6.11</v>
+        <v>4.95</v>
       </c>
       <c r="AF26">
-        <v>3.11</v>
+        <v>1.35</v>
       </c>
       <c r="AG26">
-        <v>6.27</v>
+        <v>4.95</v>
       </c>
       <c r="AH26">
-        <v>3.27</v>
+        <v>1.35</v>
       </c>
       <c r="AI26">
-        <v>6.79</v>
+        <v>5.23</v>
       </c>
       <c r="AJ26">
-        <v>3.8</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="27" spans="1:36" x14ac:dyDescent="0.25">
@@ -4076,109 +4080,109 @@
         <v>61</v>
       </c>
       <c r="B27">
-        <v>5.72</v>
+        <v>5.89</v>
       </c>
       <c r="C27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D27">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E27">
-        <v>5.77</v>
+        <v>6.5</v>
       </c>
       <c r="F27">
-        <v>0.05</v>
+        <v>0.61</v>
       </c>
       <c r="G27" s="1">
-        <v>5.98</v>
+        <v>6.01</v>
       </c>
       <c r="H27" s="1">
-        <v>0.26</v>
+        <v>0.13</v>
       </c>
       <c r="I27">
-        <v>5.96</v>
+        <v>6.3</v>
       </c>
       <c r="J27">
-        <v>0.23</v>
+        <v>0.41</v>
       </c>
       <c r="K27">
-        <v>6</v>
+        <v>6.48</v>
       </c>
       <c r="L27">
-        <v>0.28000000000000003</v>
+        <v>0.59</v>
       </c>
       <c r="M27">
-        <v>5.97</v>
+        <v>6.18</v>
       </c>
       <c r="N27">
-        <v>0.25</v>
-      </c>
-      <c r="O27" s="1">
-        <v>5.95</v>
-      </c>
-      <c r="P27" s="1">
-        <v>0.23</v>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="O27">
+        <v>6.39</v>
+      </c>
+      <c r="P27">
+        <v>0.5</v>
       </c>
       <c r="Q27">
-        <v>5.93</v>
+        <v>6.36</v>
       </c>
       <c r="R27">
-        <v>0.21</v>
+        <v>0.47</v>
       </c>
       <c r="S27">
-        <v>5.98</v>
+        <v>6.46</v>
       </c>
       <c r="T27">
-        <v>0.26</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="U27">
-        <v>6.06</v>
+        <v>6.51</v>
       </c>
       <c r="V27">
-        <v>0.34</v>
+        <v>0.62</v>
       </c>
       <c r="W27">
-        <v>5.86</v>
+        <v>6.45</v>
       </c>
       <c r="X27">
-        <v>0.14000000000000001</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="Y27">
-        <v>6.08</v>
+        <v>6.38</v>
       </c>
       <c r="Z27">
-        <v>0.36</v>
+        <v>0.49</v>
       </c>
       <c r="AA27">
-        <v>5.93</v>
+        <v>6.16</v>
       </c>
       <c r="AB27">
-        <v>0.21</v>
+        <v>0.27</v>
       </c>
       <c r="AC27">
-        <v>6.95</v>
+        <v>6.7</v>
       </c>
       <c r="AD27">
-        <v>1.22</v>
+        <v>0.81</v>
       </c>
       <c r="AE27">
-        <v>6.73</v>
+        <v>6.34</v>
       </c>
       <c r="AF27">
-        <v>1</v>
+        <v>0.45</v>
       </c>
       <c r="AG27">
-        <v>6.71</v>
+        <v>6.68</v>
       </c>
       <c r="AH27">
-        <v>0.99</v>
+        <v>0.79</v>
       </c>
       <c r="AI27">
-        <v>6.94</v>
+        <v>5.3</v>
       </c>
       <c r="AJ27">
-        <v>1.22</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="28" spans="1:36" x14ac:dyDescent="0.25">
@@ -4186,639 +4190,1771 @@
         <v>62</v>
       </c>
       <c r="B28">
-        <v>7.38</v>
+        <v>3</v>
       </c>
       <c r="C28">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D28">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E28">
-        <v>7.4</v>
+        <v>4.42</v>
       </c>
       <c r="F28">
-        <v>0.02</v>
+        <v>1.42</v>
       </c>
       <c r="G28" s="1">
-        <v>7.68</v>
+        <v>4.5</v>
       </c>
       <c r="H28" s="1">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="I28">
-        <v>7.54</v>
+        <v>4.38</v>
       </c>
       <c r="J28">
-        <v>0.16</v>
+        <v>1.39</v>
       </c>
       <c r="K28">
-        <v>7.68</v>
+        <v>4.42</v>
       </c>
       <c r="L28">
-        <v>0.3</v>
+        <v>1.42</v>
       </c>
       <c r="M28">
-        <v>7.45</v>
+        <v>5.29</v>
       </c>
       <c r="N28">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="O28" s="1">
-        <v>7.28</v>
-      </c>
-      <c r="P28" s="1">
-        <v>-0.1</v>
+        <v>2.29</v>
+      </c>
+      <c r="O28">
+        <v>5.41</v>
+      </c>
+      <c r="P28">
+        <v>2.41</v>
       </c>
       <c r="Q28">
-        <v>7.21</v>
+        <v>5.4</v>
       </c>
       <c r="R28">
-        <v>-0.17</v>
+        <v>2.4</v>
       </c>
       <c r="S28">
-        <v>7.37</v>
+        <v>5.18</v>
       </c>
       <c r="T28">
-        <v>-0.01</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="U28">
-        <v>7.62</v>
+        <v>5.4</v>
       </c>
       <c r="V28">
-        <v>0.24</v>
+        <v>2.4</v>
       </c>
       <c r="W28">
-        <v>7.27</v>
+        <v>5.42</v>
       </c>
       <c r="X28">
-        <v>-0.1</v>
+        <v>2.42</v>
       </c>
       <c r="Y28">
-        <v>7.52</v>
+        <v>5.12</v>
       </c>
       <c r="Z28">
-        <v>0.14000000000000001</v>
+        <v>2.12</v>
       </c>
       <c r="AA28">
-        <v>7.6</v>
+        <v>5.15</v>
       </c>
       <c r="AB28">
-        <v>0.22</v>
+        <v>2.15</v>
       </c>
       <c r="AC28">
-        <v>6.28</v>
+        <v>5.08</v>
       </c>
       <c r="AD28">
-        <v>-1.0900000000000001</v>
+        <v>2.08</v>
       </c>
       <c r="AE28">
-        <v>6.04</v>
+        <v>5.07</v>
       </c>
       <c r="AF28">
-        <v>-1.33</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="AG28">
-        <v>6.23</v>
+        <v>5.0599999999999996</v>
       </c>
       <c r="AH28">
-        <v>-1.1499999999999999</v>
+        <v>2.06</v>
       </c>
       <c r="AI28">
-        <v>6.79</v>
+        <v>5.33</v>
       </c>
       <c r="AJ28">
-        <v>-0.59</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="29" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>63</v>
       </c>
+      <c r="B29">
+        <v>5.72</v>
+      </c>
+      <c r="C29">
+        <v>6</v>
+      </c>
+      <c r="D29">
+        <v>6</v>
+      </c>
       <c r="E29">
-        <v>0.69799999999999995</v>
+        <v>5.87</v>
+      </c>
+      <c r="F29">
+        <v>0.15</v>
       </c>
       <c r="G29" s="1">
-        <v>0.879</v>
+        <v>6.17</v>
+      </c>
+      <c r="H29" s="1">
+        <v>0.45</v>
       </c>
       <c r="I29">
-        <v>0.80700000000000005</v>
+        <v>6.2</v>
+      </c>
+      <c r="J29">
+        <v>0.48</v>
       </c>
       <c r="K29">
-        <v>0.78200000000000003</v>
+        <v>6.24</v>
+      </c>
+      <c r="L29">
+        <v>0.52</v>
       </c>
       <c r="M29">
-        <v>0.86299999999999999</v>
-      </c>
-      <c r="O29" s="1">
-        <v>0.879</v>
+        <v>6.29</v>
+      </c>
+      <c r="N29">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="O29">
+        <v>6.14</v>
+      </c>
+      <c r="P29">
+        <v>0.42</v>
       </c>
       <c r="Q29">
-        <v>0.85</v>
+        <v>6.27</v>
+      </c>
+      <c r="R29">
+        <v>0.55000000000000004</v>
       </c>
       <c r="S29">
-        <v>0.83399999999999996</v>
+        <v>6.13</v>
+      </c>
+      <c r="T29">
+        <v>0.4</v>
       </c>
       <c r="U29">
-        <v>0.91300000000000003</v>
+        <v>6.17</v>
+      </c>
+      <c r="V29">
+        <v>0.45</v>
       </c>
       <c r="W29">
-        <v>0.88700000000000001</v>
+        <v>6.33</v>
+      </c>
+      <c r="X29">
+        <v>0.61</v>
       </c>
       <c r="Y29">
-        <v>0.91</v>
+        <v>6</v>
+      </c>
+      <c r="Z29">
+        <v>0.28000000000000003</v>
       </c>
       <c r="AA29">
-        <v>0.91300000000000003</v>
+        <v>6.44</v>
+      </c>
+      <c r="AB29">
+        <v>0.72</v>
       </c>
       <c r="AC29">
-        <v>0.81</v>
+        <v>5.85</v>
+      </c>
+      <c r="AD29">
+        <v>0.13</v>
       </c>
       <c r="AE29">
-        <v>0.83799999999999997</v>
+        <v>5.89</v>
+      </c>
+      <c r="AF29">
+        <v>0.16</v>
       </c>
       <c r="AG29">
-        <v>0.84399999999999997</v>
+        <v>5.8</v>
+      </c>
+      <c r="AH29">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="AI29">
-        <v>0.79700000000000004</v>
+        <v>6.06</v>
+      </c>
+      <c r="AJ29">
+        <v>0.34</v>
       </c>
     </row>
     <row r="30" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>64</v>
       </c>
+      <c r="B30">
+        <v>7.38</v>
+      </c>
+      <c r="C30">
+        <v>8</v>
+      </c>
+      <c r="D30">
+        <v>11</v>
+      </c>
       <c r="E30">
-        <v>14.981999999999999</v>
+        <v>7.34</v>
+      </c>
+      <c r="F30">
+        <v>-0.04</v>
       </c>
       <c r="G30" s="1">
-        <v>16.817</v>
+        <v>7.62</v>
+      </c>
+      <c r="H30" s="1">
+        <v>0.24</v>
       </c>
       <c r="I30">
-        <v>16.731999999999999</v>
+        <v>7.45</v>
+      </c>
+      <c r="J30">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K30">
-        <v>17.114999999999998</v>
+        <v>7.59</v>
+      </c>
+      <c r="L30">
+        <v>0.21</v>
       </c>
       <c r="M30">
-        <v>15.199</v>
-      </c>
-      <c r="O30" s="1">
-        <v>14.612</v>
+        <v>7.4</v>
+      </c>
+      <c r="N30">
+        <v>0.03</v>
+      </c>
+      <c r="O30">
+        <v>7.04</v>
+      </c>
+      <c r="P30">
+        <v>-0.33</v>
       </c>
       <c r="Q30">
-        <v>15.117000000000001</v>
+        <v>7.16</v>
+      </c>
+      <c r="R30">
+        <v>-0.21</v>
       </c>
       <c r="S30">
-        <v>15.664999999999999</v>
+        <v>7.22</v>
+      </c>
+      <c r="T30">
+        <v>-0.16</v>
       </c>
       <c r="U30">
-        <v>18.213000000000001</v>
+        <v>7.21</v>
+      </c>
+      <c r="V30">
+        <v>-0.17</v>
       </c>
       <c r="W30">
-        <v>16.797999999999998</v>
+        <v>7.33</v>
+      </c>
+      <c r="X30">
+        <v>-0.05</v>
       </c>
       <c r="Y30">
-        <v>17.789000000000001</v>
+        <v>7.21</v>
+      </c>
+      <c r="Z30">
+        <v>-0.17</v>
       </c>
       <c r="AA30">
-        <v>16.414000000000001</v>
+        <v>7.55</v>
+      </c>
+      <c r="AB30">
+        <v>0.17</v>
       </c>
       <c r="AC30">
-        <v>23.646999999999998</v>
+        <v>4.99</v>
+      </c>
+      <c r="AD30">
+        <v>-2.39</v>
       </c>
       <c r="AE30">
-        <v>22.413</v>
+        <v>4.97</v>
+      </c>
+      <c r="AF30">
+        <v>-2.4</v>
       </c>
       <c r="AG30">
-        <v>21.995000000000001</v>
+        <v>4.97</v>
+      </c>
+      <c r="AH30">
+        <v>-2.4</v>
       </c>
       <c r="AI30">
-        <v>25.248999999999999</v>
+        <v>5.25</v>
+      </c>
+      <c r="AJ30">
+        <v>-2.13</v>
       </c>
     </row>
     <row r="31" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>65</v>
       </c>
+      <c r="B31" t="s">
+        <v>52</v>
+      </c>
+      <c r="C31" t="s">
+        <v>52</v>
+      </c>
+      <c r="D31">
+        <v>2</v>
+      </c>
       <c r="E31">
-        <v>0.373</v>
+        <v>2</v>
       </c>
       <c r="G31" s="1">
-        <v>0.505</v>
+        <v>2</v>
       </c>
       <c r="I31">
-        <v>0.60599999999999998</v>
+        <v>2</v>
       </c>
       <c r="K31">
-        <v>0.64</v>
+        <v>2</v>
       </c>
       <c r="M31">
-        <v>0.747</v>
-      </c>
-      <c r="O31" s="1">
-        <v>0.7</v>
+        <v>2</v>
+      </c>
+      <c r="O31">
+        <v>2</v>
       </c>
       <c r="Q31">
-        <v>0.63400000000000001</v>
+        <v>2</v>
       </c>
       <c r="S31">
-        <v>0.68600000000000005</v>
+        <v>2</v>
       </c>
       <c r="U31">
-        <v>0.46100000000000002</v>
+        <v>2</v>
       </c>
       <c r="W31">
-        <v>0.35599999999999998</v>
+        <v>2</v>
       </c>
       <c r="Y31">
-        <v>0.47</v>
+        <v>2</v>
       </c>
       <c r="AA31">
-        <v>0.39100000000000001</v>
+        <v>2</v>
       </c>
       <c r="AC31">
-        <v>0.874</v>
+        <v>2</v>
       </c>
       <c r="AE31">
-        <v>0.86899999999999999</v>
+        <v>2</v>
       </c>
       <c r="AG31">
-        <v>0.91200000000000003</v>
+        <v>2</v>
       </c>
       <c r="AI31">
-        <v>0.81399999999999995</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>66</v>
       </c>
-      <c r="E32" t="s">
-        <v>67</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="I32" t="s">
-        <v>67</v>
-      </c>
-      <c r="K32" t="s">
-        <v>67</v>
-      </c>
-      <c r="M32" t="s">
-        <v>67</v>
-      </c>
-      <c r="O32" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>67</v>
-      </c>
-      <c r="S32" t="s">
-        <v>67</v>
-      </c>
-      <c r="U32" t="s">
-        <v>67</v>
-      </c>
-      <c r="W32" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y32" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA32" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC32" t="s">
-        <v>67</v>
-      </c>
-      <c r="AE32" t="s">
-        <v>67</v>
-      </c>
-      <c r="AG32" t="s">
-        <v>67</v>
-      </c>
-      <c r="AI32" t="s">
-        <v>67</v>
+      <c r="B32" t="s">
+        <v>52</v>
+      </c>
+      <c r="C32" t="s">
+        <v>52</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>3.97</v>
+      </c>
+      <c r="G32" s="1">
+        <v>3.91</v>
+      </c>
+      <c r="I32">
+        <v>3.76</v>
+      </c>
+      <c r="K32">
+        <v>3.77</v>
+      </c>
+      <c r="M32">
+        <v>3.78</v>
+      </c>
+      <c r="O32">
+        <v>3.73</v>
+      </c>
+      <c r="Q32">
+        <v>3.75</v>
+      </c>
+      <c r="S32">
+        <v>3.87</v>
+      </c>
+      <c r="U32">
+        <v>3.75</v>
+      </c>
+      <c r="W32">
+        <v>3.75</v>
+      </c>
+      <c r="Y32">
+        <v>3.88</v>
+      </c>
+      <c r="AA32">
+        <v>3.82</v>
+      </c>
+      <c r="AC32">
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="AE32">
+        <v>4.07</v>
+      </c>
+      <c r="AG32">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="AI32">
+        <v>4.42</v>
       </c>
     </row>
     <row r="33" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>68</v>
+        <v>67</v>
+      </c>
+      <c r="B33" t="s">
+        <v>52</v>
+      </c>
+      <c r="C33" t="s">
+        <v>52</v>
+      </c>
+      <c r="D33">
+        <v>9</v>
       </c>
       <c r="E33">
-        <v>0.29499999999999998</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="G33" s="1">
-        <v>0.46800000000000003</v>
+        <v>3.98</v>
       </c>
       <c r="I33">
-        <v>0.47699999999999998</v>
+        <v>3.82</v>
       </c>
       <c r="K33">
-        <v>0.47</v>
+        <v>3.83</v>
       </c>
       <c r="M33">
-        <v>0.61</v>
-      </c>
-      <c r="O33" s="1">
-        <v>0.61799999999999999</v>
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="O33">
+        <v>4.13</v>
       </c>
       <c r="Q33">
-        <v>0.57799999999999996</v>
+        <v>3.81</v>
       </c>
       <c r="S33">
-        <v>0.57899999999999996</v>
+        <v>3.93</v>
       </c>
       <c r="U33">
-        <v>0.47499999999999998</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="W33">
-        <v>0.39200000000000002</v>
+        <v>3.82</v>
       </c>
       <c r="Y33">
-        <v>0.442</v>
+        <v>4.34</v>
       </c>
       <c r="AA33">
-        <v>0.44900000000000001</v>
+        <v>3.89</v>
       </c>
       <c r="AC33">
-        <v>0.316</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="AE33">
-        <v>0.42299999999999999</v>
+        <v>4.07</v>
       </c>
       <c r="AG33">
-        <v>0.42899999999999999</v>
+        <v>4.2300000000000004</v>
       </c>
       <c r="AI33">
-        <v>0.23400000000000001</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="34" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>69</v>
-      </c>
-      <c r="E34" t="s">
-        <v>67</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="I34" t="s">
-        <v>67</v>
-      </c>
-      <c r="K34" t="s">
-        <v>67</v>
-      </c>
-      <c r="M34" t="s">
-        <v>67</v>
-      </c>
-      <c r="O34" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>67</v>
-      </c>
-      <c r="S34" t="s">
-        <v>67</v>
-      </c>
-      <c r="U34" t="s">
-        <v>67</v>
-      </c>
-      <c r="W34" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y34" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA34" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC34" t="s">
-        <v>67</v>
-      </c>
-      <c r="AE34" t="s">
-        <v>67</v>
-      </c>
-      <c r="AG34" t="s">
-        <v>67</v>
-      </c>
-      <c r="AI34" t="s">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="B34" t="s">
+        <v>52</v>
+      </c>
+      <c r="C34" t="s">
+        <v>52</v>
+      </c>
+      <c r="D34">
+        <v>3</v>
+      </c>
+      <c r="E34">
+        <v>3.83</v>
+      </c>
+      <c r="G34" s="1">
+        <v>3.76</v>
+      </c>
+      <c r="I34">
+        <v>3.62</v>
+      </c>
+      <c r="K34">
+        <v>3.61</v>
+      </c>
+      <c r="M34">
+        <v>3.62</v>
+      </c>
+      <c r="O34">
+        <v>3.59</v>
+      </c>
+      <c r="Q34">
+        <v>3.6</v>
+      </c>
+      <c r="S34">
+        <v>3.72</v>
+      </c>
+      <c r="U34">
+        <v>3.6</v>
+      </c>
+      <c r="W34">
+        <v>3.6</v>
+      </c>
+      <c r="Y34">
+        <v>3.74</v>
+      </c>
+      <c r="AA34">
+        <v>3.65</v>
+      </c>
+      <c r="AC34">
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="AE34">
+        <v>4.07</v>
+      </c>
+      <c r="AG34">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="AI34">
+        <v>4.43</v>
       </c>
     </row>
     <row r="35" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="B35" t="s">
+        <v>52</v>
+      </c>
+      <c r="C35" t="s">
+        <v>52</v>
+      </c>
+      <c r="D35">
+        <v>8</v>
       </c>
       <c r="E35">
-        <v>0.48199999999999998</v>
+        <v>3.83</v>
       </c>
       <c r="G35" s="1">
-        <v>0.60299999999999998</v>
+        <v>3.76</v>
       </c>
       <c r="I35">
-        <v>0.71199999999999997</v>
+        <v>3.61</v>
       </c>
       <c r="K35">
-        <v>0.69399999999999995</v>
+        <v>3.61</v>
       </c>
       <c r="M35">
-        <v>0.74399999999999999</v>
-      </c>
-      <c r="O35" s="1">
-        <v>0.75800000000000001</v>
+        <v>3.62</v>
+      </c>
+      <c r="O35">
+        <v>3.59</v>
       </c>
       <c r="Q35">
-        <v>0.73099999999999998</v>
+        <v>3.6</v>
       </c>
       <c r="S35">
-        <v>0.71899999999999997</v>
+        <v>3.72</v>
       </c>
       <c r="U35">
-        <v>0.49099999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="W35">
-        <v>0.48799999999999999</v>
+        <v>3.59</v>
       </c>
       <c r="Y35">
-        <v>0.501</v>
+        <v>3.73</v>
       </c>
       <c r="AA35">
-        <v>0.52100000000000002</v>
+        <v>3.65</v>
       </c>
       <c r="AC35">
-        <v>0.44900000000000001</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="AE35">
-        <v>0.56699999999999995</v>
+        <v>4.07</v>
       </c>
       <c r="AG35">
-        <v>0.56499999999999995</v>
+        <v>4.2300000000000004</v>
       </c>
       <c r="AI35">
-        <v>0.437</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="36" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>71</v>
-      </c>
-      <c r="E36" t="s">
-        <v>67</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="I36" t="s">
-        <v>67</v>
-      </c>
-      <c r="K36" t="s">
-        <v>67</v>
-      </c>
-      <c r="M36" t="s">
-        <v>67</v>
-      </c>
-      <c r="O36" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>67</v>
-      </c>
-      <c r="S36" t="s">
-        <v>67</v>
-      </c>
-      <c r="U36" t="s">
-        <v>67</v>
-      </c>
-      <c r="W36" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y36" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA36" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC36" t="s">
-        <v>67</v>
-      </c>
-      <c r="AE36" t="s">
-        <v>67</v>
-      </c>
-      <c r="AG36" t="s">
-        <v>67</v>
-      </c>
-      <c r="AI36" t="s">
-        <v>67</v>
+        <v>70</v>
+      </c>
+      <c r="B36" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" t="s">
+        <v>52</v>
+      </c>
+      <c r="D36">
+        <v>3</v>
+      </c>
+      <c r="E36">
+        <v>3.73</v>
+      </c>
+      <c r="G36" s="1">
+        <v>3.69</v>
+      </c>
+      <c r="I36">
+        <v>3.57</v>
+      </c>
+      <c r="K36">
+        <v>3.57</v>
+      </c>
+      <c r="M36">
+        <v>3.57</v>
+      </c>
+      <c r="O36">
+        <v>3.53</v>
+      </c>
+      <c r="Q36">
+        <v>3.57</v>
+      </c>
+      <c r="S36">
+        <v>3.66</v>
+      </c>
+      <c r="U36">
+        <v>3.55</v>
+      </c>
+      <c r="W36">
+        <v>3.57</v>
+      </c>
+      <c r="Y36">
+        <v>3.63</v>
+      </c>
+      <c r="AA36">
+        <v>3.62</v>
+      </c>
+      <c r="AC36">
+        <v>4.22</v>
+      </c>
+      <c r="AE36">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="AG36">
+        <v>4.29</v>
+      </c>
+      <c r="AI36">
+        <v>4.5</v>
       </c>
     </row>
     <row r="37" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>71</v>
+      </c>
+      <c r="B37" t="s">
+        <v>52</v>
+      </c>
+      <c r="C37" t="s">
+        <v>52</v>
+      </c>
+      <c r="D37">
+        <v>8</v>
+      </c>
+      <c r="E37">
+        <v>7.03</v>
+      </c>
+      <c r="G37" s="1">
+        <v>6.73</v>
+      </c>
+      <c r="I37">
+        <v>6.8</v>
+      </c>
+      <c r="K37">
+        <v>6.72</v>
+      </c>
+      <c r="M37">
+        <v>6.48</v>
+      </c>
+      <c r="O37">
+        <v>6.63</v>
+      </c>
+      <c r="Q37">
+        <v>6.56</v>
+      </c>
+      <c r="S37">
+        <v>6.53</v>
+      </c>
+      <c r="U37">
+        <v>6.55</v>
+      </c>
+      <c r="W37">
+        <v>6.45</v>
+      </c>
+      <c r="Y37">
+        <v>6.7</v>
+      </c>
+      <c r="AA37">
+        <v>6.47</v>
+      </c>
+      <c r="AC37">
+        <v>9.73</v>
+      </c>
+      <c r="AE37">
+        <v>9.92</v>
+      </c>
+      <c r="AG37">
+        <v>9.76</v>
+      </c>
+      <c r="AI37">
+        <v>9.61</v>
+      </c>
+    </row>
+    <row r="38" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>72</v>
       </c>
-      <c r="E37">
-        <v>0.63200000000000001</v>
-      </c>
-      <c r="G37" s="1">
-        <v>0.66700000000000004</v>
-      </c>
-      <c r="I37">
-        <v>0.66800000000000004</v>
-      </c>
-      <c r="K37">
-        <v>0.71299999999999997</v>
-      </c>
-      <c r="M37">
-        <v>0.88500000000000001</v>
-      </c>
-      <c r="O37" s="1">
-        <v>0.88800000000000001</v>
-      </c>
-      <c r="Q37">
-        <v>0.92</v>
-      </c>
-      <c r="S37">
-        <v>0.92400000000000004</v>
-      </c>
-      <c r="U37">
-        <v>0.93100000000000005</v>
-      </c>
-      <c r="W37">
-        <v>0.95099999999999996</v>
-      </c>
-      <c r="Y37">
-        <v>0.95799999999999996</v>
-      </c>
-      <c r="AA37">
-        <v>1.012</v>
-      </c>
-      <c r="AC37">
-        <v>1.286</v>
-      </c>
-      <c r="AE37">
-        <v>1.42</v>
-      </c>
-      <c r="AG37">
-        <v>1.4219999999999999</v>
-      </c>
-      <c r="AI37">
-        <v>1.448</v>
+      <c r="B38" t="s">
+        <v>52</v>
+      </c>
+      <c r="C38" t="s">
+        <v>52</v>
+      </c>
+      <c r="D38">
+        <v>7</v>
+      </c>
+      <c r="E38">
+        <v>7</v>
+      </c>
+      <c r="G38" s="1">
+        <v>7</v>
+      </c>
+      <c r="I38">
+        <v>7</v>
+      </c>
+      <c r="K38">
+        <v>7</v>
+      </c>
+      <c r="M38">
+        <v>7</v>
+      </c>
+      <c r="O38">
+        <v>7</v>
+      </c>
+      <c r="Q38">
+        <v>7</v>
+      </c>
+      <c r="S38">
+        <v>7</v>
+      </c>
+      <c r="U38">
+        <v>7</v>
+      </c>
+      <c r="W38">
+        <v>7</v>
+      </c>
+      <c r="Y38">
+        <v>7</v>
+      </c>
+      <c r="AA38">
+        <v>7</v>
+      </c>
+      <c r="AC38">
+        <v>7</v>
+      </c>
+      <c r="AE38">
+        <v>7</v>
+      </c>
+      <c r="AG38">
+        <v>7</v>
+      </c>
+      <c r="AI38">
+        <v>7</v>
       </c>
     </row>
-    <row r="38" spans="1:35" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+    <row r="39" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>73</v>
       </c>
-      <c r="E38">
-        <v>1.06</v>
-      </c>
-      <c r="G38" s="1">
-        <v>1.0209999999999999</v>
-      </c>
-      <c r="I38">
+      <c r="B39" t="s">
+        <v>52</v>
+      </c>
+      <c r="C39" t="s">
+        <v>52</v>
+      </c>
+      <c r="D39">
+        <v>4</v>
+      </c>
+      <c r="E39">
+        <v>4</v>
+      </c>
+      <c r="G39" s="1">
+        <v>4</v>
+      </c>
+      <c r="I39">
+        <v>4</v>
+      </c>
+      <c r="K39">
+        <v>4</v>
+      </c>
+      <c r="M39">
+        <v>4</v>
+      </c>
+      <c r="O39">
+        <v>4</v>
+      </c>
+      <c r="Q39">
+        <v>4</v>
+      </c>
+      <c r="S39">
+        <v>4</v>
+      </c>
+      <c r="U39">
+        <v>4</v>
+      </c>
+      <c r="W39">
+        <v>4</v>
+      </c>
+      <c r="Y39">
+        <v>4</v>
+      </c>
+      <c r="AA39">
+        <v>4</v>
+      </c>
+      <c r="AC39">
+        <v>4</v>
+      </c>
+      <c r="AE39">
+        <v>4</v>
+      </c>
+      <c r="AG39">
+        <v>4</v>
+      </c>
+      <c r="AI39">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>74</v>
+      </c>
+      <c r="B40" t="s">
+        <v>52</v>
+      </c>
+      <c r="C40" t="s">
+        <v>52</v>
+      </c>
+      <c r="D40">
+        <v>4</v>
+      </c>
+      <c r="E40">
+        <v>3.74</v>
+      </c>
+      <c r="G40" s="1">
+        <v>3.87</v>
+      </c>
+      <c r="I40">
+        <v>3.95</v>
+      </c>
+      <c r="K40">
+        <v>3.95</v>
+      </c>
+      <c r="M40">
+        <v>3.85</v>
+      </c>
+      <c r="O40">
+        <v>3.83</v>
+      </c>
+      <c r="Q40">
+        <v>4.03</v>
+      </c>
+      <c r="S40">
+        <v>3.85</v>
+      </c>
+      <c r="U40">
+        <v>3.82</v>
+      </c>
+      <c r="W40">
+        <v>4.03</v>
+      </c>
+      <c r="Y40">
+        <v>3.57</v>
+      </c>
+      <c r="AA40">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="AC40">
+        <v>5.51</v>
+      </c>
+      <c r="AE40">
+        <v>5.52</v>
+      </c>
+      <c r="AG40">
+        <v>5.46</v>
+      </c>
+      <c r="AI40">
+        <v>5.74</v>
+      </c>
+    </row>
+    <row r="41" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>75</v>
+      </c>
+      <c r="B41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C41" t="s">
+        <v>52</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41">
+        <v>3.92</v>
+      </c>
+      <c r="G41" s="1">
+        <v>4.05</v>
+      </c>
+      <c r="I41">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="K41">
+        <v>4.07</v>
+      </c>
+      <c r="M41">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="O41">
+        <v>4.05</v>
+      </c>
+      <c r="Q41">
+        <v>4.2</v>
+      </c>
+      <c r="S41">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="U41">
+        <v>4.01</v>
+      </c>
+      <c r="W41">
+        <v>4.17</v>
+      </c>
+      <c r="Y41">
+        <v>3.84</v>
+      </c>
+      <c r="AA41">
+        <v>4.22</v>
+      </c>
+      <c r="AC41">
+        <v>5.37</v>
+      </c>
+      <c r="AE41">
+        <v>5.37</v>
+      </c>
+      <c r="AG41">
+        <v>5.33</v>
+      </c>
+      <c r="AI41">
+        <v>5.61</v>
+      </c>
+    </row>
+    <row r="42" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>76</v>
+      </c>
+      <c r="B42" t="s">
+        <v>52</v>
+      </c>
+      <c r="C42" t="s">
+        <v>52</v>
+      </c>
+      <c r="D42">
+        <v>11</v>
+      </c>
+      <c r="E42">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="G42" s="1">
+        <v>5.21</v>
+      </c>
+      <c r="I42">
+        <v>5.2</v>
+      </c>
+      <c r="K42">
+        <v>5.13</v>
+      </c>
+      <c r="M42">
+        <v>5.12</v>
+      </c>
+      <c r="O42">
+        <v>5.09</v>
+      </c>
+      <c r="Q42">
+        <v>5.18</v>
+      </c>
+      <c r="S42">
+        <v>5.13</v>
+      </c>
+      <c r="U42">
+        <v>5.0199999999999996</v>
+      </c>
+      <c r="W42">
+        <v>5.13</v>
+      </c>
+      <c r="Y42">
+        <v>5</v>
+      </c>
+      <c r="AA42">
+        <v>5.22</v>
+      </c>
+      <c r="AC42">
+        <v>5.69</v>
+      </c>
+      <c r="AE42">
+        <v>5.71</v>
+      </c>
+      <c r="AG42">
+        <v>5.64</v>
+      </c>
+      <c r="AI42">
+        <v>5.91</v>
+      </c>
+    </row>
+    <row r="43" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>77</v>
+      </c>
+      <c r="B43" t="s">
+        <v>52</v>
+      </c>
+      <c r="C43" t="s">
+        <v>52</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+      <c r="E43">
+        <v>4.12</v>
+      </c>
+      <c r="G43" s="1">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="I43">
+        <v>4.04</v>
+      </c>
+      <c r="K43">
+        <v>4</v>
+      </c>
+      <c r="M43">
+        <v>4</v>
+      </c>
+      <c r="O43">
+        <v>3.99</v>
+      </c>
+      <c r="Q43">
+        <v>4.04</v>
+      </c>
+      <c r="S43">
+        <v>4.08</v>
+      </c>
+      <c r="U43">
+        <v>3.96</v>
+      </c>
+      <c r="W43">
+        <v>4.01</v>
+      </c>
+      <c r="Y43">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="AA43">
+        <v>4.07</v>
+      </c>
+      <c r="AC43">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="AE43">
+        <v>4.6100000000000003</v>
+      </c>
+      <c r="AG43">
+        <v>4.66</v>
+      </c>
+      <c r="AI43">
+        <v>4.93</v>
+      </c>
+    </row>
+    <row r="44" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>78</v>
+      </c>
+      <c r="E44">
+        <v>0.83199999999999996</v>
+      </c>
+      <c r="G44" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="I44">
+        <v>0.82199999999999995</v>
+      </c>
+      <c r="K44">
+        <v>0.81599999999999995</v>
+      </c>
+      <c r="M44">
+        <v>0.84599999999999997</v>
+      </c>
+      <c r="O44">
+        <v>0.85599999999999998</v>
+      </c>
+      <c r="Q44">
+        <v>0.84899999999999998</v>
+      </c>
+      <c r="S44">
+        <v>0.84599999999999997</v>
+      </c>
+      <c r="U44">
+        <v>0.85699999999999998</v>
+      </c>
+      <c r="W44">
+        <v>0.84599999999999997</v>
+      </c>
+      <c r="Y44">
+        <v>0.86299999999999999</v>
+      </c>
+      <c r="AA44">
+        <v>0.84699999999999998</v>
+      </c>
+      <c r="AC44">
+        <v>0.77500000000000002</v>
+      </c>
+      <c r="AE44">
+        <v>0.79300000000000004</v>
+      </c>
+      <c r="AG44">
+        <v>0.79700000000000004</v>
+      </c>
+      <c r="AI44">
+        <v>0.75900000000000001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>79</v>
+      </c>
+      <c r="E45">
+        <v>21.827999999999999</v>
+      </c>
+      <c r="G45" s="1">
+        <v>21.143000000000001</v>
+      </c>
+      <c r="I45">
+        <v>21.67</v>
+      </c>
+      <c r="K45">
+        <v>21.869</v>
+      </c>
+      <c r="M45">
+        <v>23.097999999999999</v>
+      </c>
+      <c r="O45">
+        <v>22.2</v>
+      </c>
+      <c r="Q45">
+        <v>22.398</v>
+      </c>
+      <c r="S45">
+        <v>22.753</v>
+      </c>
+      <c r="U45">
+        <v>22.14</v>
+      </c>
+      <c r="W45">
+        <v>22.826000000000001</v>
+      </c>
+      <c r="Y45">
+        <v>21.951000000000001</v>
+      </c>
+      <c r="AA45">
+        <v>22.622</v>
+      </c>
+      <c r="AC45">
+        <v>26.437000000000001</v>
+      </c>
+      <c r="AE45">
+        <v>25.946999999999999</v>
+      </c>
+      <c r="AG45">
+        <v>25.587</v>
+      </c>
+      <c r="AI45">
+        <v>28.625</v>
+      </c>
+    </row>
+    <row r="46" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>80</v>
+      </c>
+      <c r="E46">
+        <v>0.35299999999999998</v>
+      </c>
+      <c r="G46" s="1">
+        <v>0.45900000000000002</v>
+      </c>
+      <c r="I46">
+        <v>0.46100000000000002</v>
+      </c>
+      <c r="K46">
+        <v>0.47499999999999998</v>
+      </c>
+      <c r="M46">
+        <v>0.40200000000000002</v>
+      </c>
+      <c r="O46">
+        <v>0.45500000000000002</v>
+      </c>
+      <c r="Q46">
+        <v>0.40699999999999997</v>
+      </c>
+      <c r="S46">
+        <v>0.36499999999999999</v>
+      </c>
+      <c r="U46">
+        <v>0.45200000000000001</v>
+      </c>
+      <c r="W46">
+        <v>0.39300000000000002</v>
+      </c>
+      <c r="Y46">
+        <v>0.38200000000000001</v>
+      </c>
+      <c r="AA46">
+        <v>0.375</v>
+      </c>
+      <c r="AC46">
+        <v>0.74299999999999999</v>
+      </c>
+      <c r="AE46">
+        <v>0.74</v>
+      </c>
+      <c r="AG46">
+        <v>0.76100000000000001</v>
+      </c>
+      <c r="AI46">
+        <v>0.71099999999999997</v>
+      </c>
+    </row>
+    <row r="47" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>81</v>
+      </c>
+      <c r="E47" t="s">
+        <v>82</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="I47" t="s">
+        <v>82</v>
+      </c>
+      <c r="K47" t="s">
+        <v>82</v>
+      </c>
+      <c r="M47" t="s">
+        <v>82</v>
+      </c>
+      <c r="O47" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>82</v>
+      </c>
+      <c r="S47" t="s">
+        <v>82</v>
+      </c>
+      <c r="U47" t="s">
+        <v>82</v>
+      </c>
+      <c r="W47" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>82</v>
+      </c>
+      <c r="AA47" t="s">
+        <v>82</v>
+      </c>
+      <c r="AC47" t="s">
+        <v>82</v>
+      </c>
+      <c r="AE47" t="s">
+        <v>82</v>
+      </c>
+      <c r="AG47" t="s">
+        <v>82</v>
+      </c>
+      <c r="AI47" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="48" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>83</v>
+      </c>
+      <c r="E48">
+        <v>0.34100000000000003</v>
+      </c>
+      <c r="G48" s="1">
+        <v>0.49</v>
+      </c>
+      <c r="I48">
+        <v>0.39100000000000001</v>
+      </c>
+      <c r="K48">
+        <v>0.38600000000000001</v>
+      </c>
+      <c r="M48">
+        <v>0.374</v>
+      </c>
+      <c r="O48">
+        <v>0.42799999999999999</v>
+      </c>
+      <c r="Q48">
+        <v>0.379</v>
+      </c>
+      <c r="S48">
+        <v>0.36299999999999999</v>
+      </c>
+      <c r="U48">
+        <v>0.41899999999999998</v>
+      </c>
+      <c r="W48">
+        <v>0.35299999999999998</v>
+      </c>
+      <c r="Y48">
+        <v>0.433</v>
+      </c>
+      <c r="AA48">
+        <v>0.34699999999999998</v>
+      </c>
+      <c r="AC48">
+        <v>0.29299999999999998</v>
+      </c>
+      <c r="AE48">
+        <v>0.373</v>
+      </c>
+      <c r="AG48">
+        <v>0.377</v>
+      </c>
+      <c r="AI48">
+        <v>0.23899999999999999</v>
+      </c>
+    </row>
+    <row r="49" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>84</v>
+      </c>
+      <c r="E49" t="s">
+        <v>82</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="I49" t="s">
+        <v>82</v>
+      </c>
+      <c r="K49" t="s">
+        <v>82</v>
+      </c>
+      <c r="M49" t="s">
+        <v>82</v>
+      </c>
+      <c r="O49" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>82</v>
+      </c>
+      <c r="S49" t="s">
+        <v>82</v>
+      </c>
+      <c r="U49" t="s">
+        <v>82</v>
+      </c>
+      <c r="W49" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>82</v>
+      </c>
+      <c r="AA49" t="s">
+        <v>82</v>
+      </c>
+      <c r="AC49" t="s">
+        <v>82</v>
+      </c>
+      <c r="AE49" t="s">
+        <v>82</v>
+      </c>
+      <c r="AG49" t="s">
+        <v>82</v>
+      </c>
+      <c r="AI49" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="50" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>85</v>
+      </c>
+      <c r="E50">
+        <v>0.50700000000000001</v>
+      </c>
+      <c r="G50" s="1">
+        <v>0.55500000000000005</v>
+      </c>
+      <c r="I50">
+        <v>0.52800000000000002</v>
+      </c>
+      <c r="K50">
+        <v>0.52200000000000002</v>
+      </c>
+      <c r="M50">
+        <v>0.38700000000000001</v>
+      </c>
+      <c r="O50">
+        <v>0.47299999999999998</v>
+      </c>
+      <c r="Q50">
+        <v>0.42099999999999999</v>
+      </c>
+      <c r="S50">
+        <v>0.39200000000000002</v>
+      </c>
+      <c r="U50">
+        <v>0.45100000000000001</v>
+      </c>
+      <c r="W50">
+        <v>0.38800000000000001</v>
+      </c>
+      <c r="Y50">
+        <v>0.46100000000000002</v>
+      </c>
+      <c r="AA50">
+        <v>0.38800000000000001</v>
+      </c>
+      <c r="AC50">
+        <v>0.39500000000000002</v>
+      </c>
+      <c r="AE50">
+        <v>0.45600000000000002</v>
+      </c>
+      <c r="AG50">
+        <v>0.44800000000000001</v>
+      </c>
+      <c r="AI50">
+        <v>0.36499999999999999</v>
+      </c>
+    </row>
+    <row r="51" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>86</v>
+      </c>
+      <c r="E51" t="s">
+        <v>82</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="I51" t="s">
+        <v>82</v>
+      </c>
+      <c r="K51" t="s">
+        <v>82</v>
+      </c>
+      <c r="M51" t="s">
+        <v>82</v>
+      </c>
+      <c r="O51" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>82</v>
+      </c>
+      <c r="S51" t="s">
+        <v>82</v>
+      </c>
+      <c r="U51" t="s">
+        <v>82</v>
+      </c>
+      <c r="W51" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>82</v>
+      </c>
+      <c r="AA51" t="s">
+        <v>82</v>
+      </c>
+      <c r="AC51" t="s">
+        <v>82</v>
+      </c>
+      <c r="AE51" t="s">
+        <v>82</v>
+      </c>
+      <c r="AG51" t="s">
+        <v>82</v>
+      </c>
+      <c r="AI51" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="52" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>87</v>
+      </c>
+      <c r="E52">
+        <v>0.70699999999999996</v>
+      </c>
+      <c r="G52" s="1">
+        <v>0.71399999999999997</v>
+      </c>
+      <c r="I52">
+        <v>0.76700000000000002</v>
+      </c>
+      <c r="K52">
+        <v>0.81599999999999995</v>
+      </c>
+      <c r="M52">
+        <v>1</v>
+      </c>
+      <c r="O52">
+        <v>1</v>
+      </c>
+      <c r="Q52">
+        <v>1.006</v>
+      </c>
+      <c r="S52">
+        <v>1.016</v>
+      </c>
+      <c r="U52">
         <v>1.0169999999999999</v>
       </c>
-      <c r="K38">
-        <v>1.0009999999999999</v>
-      </c>
-      <c r="M38">
-        <v>1.1859999999999999</v>
-      </c>
-      <c r="O38" s="1">
+      <c r="W52">
+        <v>1.02</v>
+      </c>
+      <c r="Y52">
+        <v>1.02</v>
+      </c>
+      <c r="AA52">
+        <v>1.024</v>
+      </c>
+      <c r="AC52">
+        <v>1.2490000000000001</v>
+      </c>
+      <c r="AE52">
+        <v>1.41</v>
+      </c>
+      <c r="AG52">
+        <v>1.4119999999999999</v>
+      </c>
+      <c r="AI52">
+        <v>1.504</v>
+      </c>
+    </row>
+    <row r="53" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>88</v>
+      </c>
+      <c r="E53">
+        <v>1.0960000000000001</v>
+      </c>
+      <c r="G53" s="1">
+        <v>1.044</v>
+      </c>
+      <c r="I53">
+        <v>1.107</v>
+      </c>
+      <c r="K53">
+        <v>1.121</v>
+      </c>
+      <c r="M53">
+        <v>1.371</v>
+      </c>
+      <c r="O53">
+        <v>1.3640000000000001</v>
+      </c>
+      <c r="Q53">
+        <v>1.377</v>
+      </c>
+      <c r="S53">
+        <v>1.391</v>
+      </c>
+      <c r="U53">
+        <v>1.3640000000000001</v>
+      </c>
+      <c r="W53">
+        <v>1.3759999999999999</v>
+      </c>
+      <c r="Y53">
+        <v>1.4019999999999999</v>
+      </c>
+      <c r="AA53">
+        <v>1.3919999999999999</v>
+      </c>
+      <c r="AC53">
+        <v>1.5820000000000001</v>
+      </c>
+      <c r="AE53">
+        <v>1.702</v>
+      </c>
+      <c r="AG53">
+        <v>1.659</v>
+      </c>
+      <c r="AI53">
+        <v>1.871</v>
+      </c>
+    </row>
+    <row r="54" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>89</v>
+      </c>
+      <c r="E54">
+        <v>1.022</v>
+      </c>
+      <c r="G54" s="1">
+        <v>0.998</v>
+      </c>
+      <c r="I54">
+        <v>0.97699999999999998</v>
+      </c>
+      <c r="K54">
+        <v>0.96199999999999997</v>
+      </c>
+      <c r="M54">
+        <v>1.2030000000000001</v>
+      </c>
+      <c r="O54">
+        <v>1.2050000000000001</v>
+      </c>
+      <c r="Q54">
         <v>1.2010000000000001</v>
       </c>
-      <c r="Q38">
-        <v>1.2230000000000001</v>
-      </c>
-      <c r="S38">
-        <v>1.212</v>
-      </c>
-      <c r="U38">
-        <v>1.2</v>
-      </c>
-      <c r="W38">
-        <v>1.258</v>
-      </c>
-      <c r="Y38">
-        <v>1.2210000000000001</v>
-      </c>
-      <c r="AA38">
+      <c r="S54">
+        <v>1.216</v>
+      </c>
+      <c r="U54">
+        <v>1.1890000000000001</v>
+      </c>
+      <c r="W54">
+        <v>1.1850000000000001</v>
+      </c>
+      <c r="Y54">
+        <v>1.238</v>
+      </c>
+      <c r="AA54">
+        <v>1.2030000000000001</v>
+      </c>
+      <c r="AC54">
+        <v>1.5429999999999999</v>
+      </c>
+      <c r="AE54">
+        <v>1.724</v>
+      </c>
+      <c r="AG54">
+        <v>1.716</v>
+      </c>
+      <c r="AI54">
+        <v>1.8220000000000001</v>
+      </c>
+    </row>
+    <row r="55" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>90</v>
+      </c>
+      <c r="E55">
+        <v>1.3560000000000001</v>
+      </c>
+      <c r="G55" s="1">
         <v>1.3</v>
       </c>
-      <c r="AC38">
-        <v>1.5349999999999999</v>
-      </c>
-      <c r="AE38">
-        <v>1.6639999999999999</v>
-      </c>
-      <c r="AG38">
-        <v>1.625</v>
-      </c>
-      <c r="AI38">
-        <v>1.6839999999999999</v>
+      <c r="I55">
+        <v>1.3520000000000001</v>
+      </c>
+      <c r="K55">
+        <v>1.343</v>
+      </c>
+      <c r="M55">
+        <v>1.5820000000000001</v>
+      </c>
+      <c r="O55">
+        <v>1.577</v>
+      </c>
+      <c r="Q55">
+        <v>1.5860000000000001</v>
+      </c>
+      <c r="S55">
+        <v>1.601</v>
+      </c>
+      <c r="U55">
+        <v>1.5589999999999999</v>
+      </c>
+      <c r="W55">
+        <v>1.5669999999999999</v>
+      </c>
+      <c r="Y55">
+        <v>1.6140000000000001</v>
+      </c>
+      <c r="AA55">
+        <v>1.6060000000000001</v>
+      </c>
+      <c r="AC55">
+        <v>2.04</v>
+      </c>
+      <c r="AE55">
+        <v>2.1469999999999998</v>
+      </c>
+      <c r="AG55">
+        <v>2.097</v>
+      </c>
+      <c r="AI55">
+        <v>2.3450000000000002</v>
       </c>
     </row>
   </sheetData>
